--- a/TKB toàn trường CHECK - chuẩn.xlsx
+++ b/TKB toàn trường CHECK - chuẩn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trang\Desktop\UNIGO 2026-2027\TKB toàn trường\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD8405-F845-4F3B-88D1-5272238A4B63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5A0503-517B-4D50-9245-01124FF2F2FD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="184">
   <si>
     <t>THỨ</t>
   </si>
@@ -531,9 +531,6 @@
     <t>Nhạc -TTH3</t>
   </si>
   <si>
-    <t>GDTC - TTH3</t>
-  </si>
-  <si>
     <t>TDNN - Nhi</t>
   </si>
   <si>
@@ -583,6 +580,9 @@
   </si>
   <si>
     <t>PHT THƯỜNG TRỰC</t>
+  </si>
+  <si>
+    <t>Thanh</t>
   </si>
 </sst>
 </file>
@@ -1227,38 +1227,25 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1275,6 +1262,76 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1288,36 +1345,38 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1331,65 +1390,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1807,13 +1807,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1848,11 +1848,11 @@
       </c>
     </row>
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1908,80 +1908,80 @@
       <c r="AB3" s="2"/>
     </row>
     <row r="4" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="B4" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="78"/>
-      <c r="E4" s="77" t="s">
+      <c r="D4" s="95"/>
+      <c r="E4" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="77" t="s">
+      <c r="F4" s="95"/>
+      <c r="G4" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="78"/>
-      <c r="I4" s="77" t="s">
+      <c r="H4" s="95"/>
+      <c r="I4" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="78"/>
-      <c r="K4" s="85" t="s">
+      <c r="J4" s="95"/>
+      <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="77" t="s">
+      <c r="L4" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="N4" s="78"/>
-      <c r="O4" s="77" t="s">
+      <c r="N4" s="95"/>
+      <c r="O4" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="77" t="s">
+      <c r="P4" s="95"/>
+      <c r="Q4" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="R4" s="78"/>
-      <c r="S4" s="77" t="s">
+      <c r="R4" s="95"/>
+      <c r="S4" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="T4" s="78"/>
-      <c r="U4" s="85" t="s">
+      <c r="T4" s="95"/>
+      <c r="U4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="V4" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="77" t="s">
+      <c r="V4" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="78"/>
-      <c r="Y4" s="77" t="s">
+      <c r="X4" s="95"/>
+      <c r="Y4" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="76" t="s">
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="AB4" s="76"/>
-      <c r="AC4" s="80" t="s">
+      <c r="AB4" s="97"/>
+      <c r="AC4" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="AD4" s="81"/>
-      <c r="AE4" s="80" t="s">
+      <c r="AD4" s="92"/>
+      <c r="AE4" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="AF4" s="81"/>
-      <c r="AG4" s="85" t="s">
+      <c r="AF4" s="92"/>
+      <c r="AG4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="AH4" s="85" t="s">
+      <c r="AH4" s="82" t="s">
         <v>1</v>
       </c>
       <c r="AI4" s="67" t="s">
@@ -2006,8 +2006,8 @@
       <c r="AR4" s="68"/>
     </row>
     <row r="5" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
+      <c r="A5" s="83"/>
+      <c r="B5" s="83"/>
       <c r="C5" s="58" t="s">
         <v>3</v>
       </c>
@@ -2032,8 +2032,8 @@
       <c r="J5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
       <c r="M5" s="58" t="s">
         <v>3</v>
       </c>
@@ -2058,8 +2058,8 @@
       <c r="T5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="U5" s="86"/>
-      <c r="V5" s="86"/>
+      <c r="U5" s="83"/>
+      <c r="V5" s="83"/>
       <c r="W5" s="58" t="s">
         <v>3</v>
       </c>
@@ -2090,8 +2090,8 @@
       <c r="AF5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="AG5" s="86"/>
-      <c r="AH5" s="86"/>
+      <c r="AG5" s="83"/>
+      <c r="AH5" s="83"/>
       <c r="AI5" s="62" t="s">
         <v>3</v>
       </c>
@@ -2124,7 +2124,7 @@
       </c>
     </row>
     <row r="6" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="87">
+      <c r="A6" s="84">
         <v>2</v>
       </c>
       <c r="B6" s="4">
@@ -2154,7 +2154,7 @@
       <c r="J6" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="K6" s="87">
+      <c r="K6" s="84">
         <v>2</v>
       </c>
       <c r="L6" s="4">
@@ -2184,7 +2184,7 @@
       <c r="T6" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="U6" s="87">
+      <c r="U6" s="84">
         <v>2</v>
       </c>
       <c r="V6" s="4">
@@ -2194,13 +2194,13 @@
         <v>127</v>
       </c>
       <c r="X6" s="72" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="Y6" s="72" t="s">
         <v>54</v>
       </c>
       <c r="Z6" s="72" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AA6" s="72" t="s">
         <v>111</v>
@@ -2220,7 +2220,7 @@
       <c r="AF6" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="AG6" s="87">
+      <c r="AG6" s="84">
         <v>2</v>
       </c>
       <c r="AH6" s="4">
@@ -2237,14 +2237,14 @@
       <c r="AM6" s="51"/>
       <c r="AN6" s="52"/>
       <c r="AO6" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AP6" s="52"/>
       <c r="AQ6" s="51"/>
       <c r="AR6" s="52"/>
     </row>
     <row r="7" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="88"/>
+      <c r="A7" s="85"/>
       <c r="B7" s="6">
         <v>2</v>
       </c>
@@ -2272,7 +2272,7 @@
       <c r="J7" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="K7" s="88"/>
+      <c r="K7" s="85"/>
       <c r="L7" s="6">
         <v>2</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="T7" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="U7" s="88"/>
+      <c r="U7" s="85"/>
       <c r="V7" s="6">
         <v>2</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>108</v>
       </c>
       <c r="Z7" s="72" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="AA7" s="72" t="s">
         <v>57</v>
@@ -2334,7 +2334,7 @@
       <c r="AF7" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AG7" s="88"/>
+      <c r="AG7" s="85"/>
       <c r="AH7" s="6">
         <v>2</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>61</v>
       </c>
       <c r="AK7" s="51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AL7" s="51"/>
       <c r="AM7" s="51"/>
@@ -2356,11 +2356,11 @@
       <c r="AP7" s="51"/>
       <c r="AQ7" s="51"/>
       <c r="AR7" s="51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="88"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="6">
         <v>3</v>
       </c>
@@ -2388,7 +2388,7 @@
       <c r="J8" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="88"/>
+      <c r="K8" s="85"/>
       <c r="L8" s="6">
         <v>3</v>
       </c>
@@ -2416,7 +2416,7 @@
       <c r="T8" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="U8" s="88"/>
+      <c r="U8" s="85"/>
       <c r="V8" s="6">
         <v>3</v>
       </c>
@@ -2450,7 +2450,7 @@
       <c r="AF8" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="AG8" s="88"/>
+      <c r="AG8" s="85"/>
       <c r="AH8" s="6">
         <v>3</v>
       </c>
@@ -2463,14 +2463,14 @@
       <c r="AK8" s="51"/>
       <c r="AL8" s="51"/>
       <c r="AM8" s="51" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN8" s="51" t="s">
         <v>153</v>
       </c>
       <c r="AO8" s="51"/>
       <c r="AP8" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AQ8" s="51" t="s">
         <v>153</v>
@@ -2478,7 +2478,7 @@
       <c r="AR8" s="51"/>
     </row>
     <row r="9" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="88"/>
+      <c r="A9" s="85"/>
       <c r="B9" s="6">
         <v>4</v>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="J9" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="K9" s="88"/>
+      <c r="K9" s="85"/>
       <c r="L9" s="6">
         <v>4</v>
       </c>
@@ -2534,7 +2534,7 @@
       <c r="T9" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="U9" s="88"/>
+      <c r="U9" s="85"/>
       <c r="V9" s="6">
         <v>4</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>108</v>
       </c>
       <c r="X9" s="72" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="Y9" s="72" t="s">
         <v>59</v>
@@ -2557,7 +2557,7 @@
         <v>158</v>
       </c>
       <c r="AC9" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AD9" s="72" t="s">
         <v>7</v>
@@ -2566,9 +2566,9 @@
         <v>7</v>
       </c>
       <c r="AF9" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="AG9" s="88"/>
+        <v>172</v>
+      </c>
+      <c r="AG9" s="85"/>
       <c r="AH9" s="6">
         <v>4</v>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="AR9" s="51"/>
     </row>
     <row r="10" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="89"/>
+      <c r="A10" s="86"/>
       <c r="B10" s="7">
         <v>5</v>
       </c>
@@ -2602,7 +2602,7 @@
       <c r="H10" s="72"/>
       <c r="I10" s="72"/>
       <c r="J10" s="72"/>
-      <c r="K10" s="89"/>
+      <c r="K10" s="86"/>
       <c r="L10" s="7">
         <v>5</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="R10" s="72"/>
       <c r="S10" s="72"/>
       <c r="T10" s="72"/>
-      <c r="U10" s="89"/>
+      <c r="U10" s="86"/>
       <c r="V10" s="7">
         <v>5</v>
       </c>
@@ -2634,7 +2634,7 @@
       <c r="AD10" s="72"/>
       <c r="AE10" s="72"/>
       <c r="AF10" s="72"/>
-      <c r="AG10" s="89"/>
+      <c r="AG10" s="86"/>
       <c r="AH10" s="7">
         <v>5</v>
       </c>
@@ -2650,7 +2650,7 @@
       <c r="AR10" s="52"/>
     </row>
     <row r="11" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="82">
+      <c r="A11" s="87">
         <v>3</v>
       </c>
       <c r="B11" s="4">
@@ -2680,14 +2680,14 @@
       <c r="J11" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="82">
+      <c r="K11" s="87">
         <v>3</v>
       </c>
       <c r="L11" s="4">
         <v>1</v>
       </c>
       <c r="M11" s="72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N11" s="72" t="s">
         <v>99</v>
@@ -2710,7 +2710,7 @@
       <c r="T11" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="U11" s="82">
+      <c r="U11" s="87">
         <v>3</v>
       </c>
       <c r="V11" s="4">
@@ -2746,7 +2746,7 @@
       <c r="AF11" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="AG11" s="82">
+      <c r="AG11" s="87">
         <v>3</v>
       </c>
       <c r="AH11" s="4">
@@ -2758,19 +2758,21 @@
       <c r="AJ11" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="AK11" s="51"/>
+      <c r="AK11" s="51" t="s">
+        <v>153</v>
+      </c>
       <c r="AL11" s="52"/>
       <c r="AM11" s="51"/>
       <c r="AN11" s="52"/>
       <c r="AO11" s="51"/>
       <c r="AP11" s="52"/>
       <c r="AQ11" s="51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AR11" s="52"/>
     </row>
     <row r="12" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="6">
         <v>2</v>
       </c>
@@ -2798,7 +2800,7 @@
       <c r="J12" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="K12" s="83"/>
+      <c r="K12" s="88"/>
       <c r="L12" s="6">
         <v>2</v>
       </c>
@@ -2826,7 +2828,7 @@
       <c r="T12" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="U12" s="83"/>
+      <c r="U12" s="88"/>
       <c r="V12" s="6">
         <v>2</v>
       </c>
@@ -2860,7 +2862,7 @@
       <c r="AF12" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="AG12" s="83"/>
+      <c r="AG12" s="88"/>
       <c r="AH12" s="6">
         <v>2</v>
       </c>
@@ -2871,7 +2873,7 @@
         <v>146</v>
       </c>
       <c r="AK12" s="51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AL12" s="51"/>
       <c r="AM12" s="51"/>
@@ -2880,13 +2882,13 @@
       </c>
       <c r="AO12" s="51"/>
       <c r="AP12" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AQ12" s="51"/>
       <c r="AR12" s="51"/>
     </row>
     <row r="13" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="83"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="6">
         <v>3</v>
       </c>
@@ -2914,7 +2916,7 @@
       <c r="J13" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="83"/>
+      <c r="K13" s="88"/>
       <c r="L13" s="6">
         <v>3</v>
       </c>
@@ -2942,7 +2944,7 @@
       <c r="T13" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="U13" s="83"/>
+      <c r="U13" s="88"/>
       <c r="V13" s="6">
         <v>3</v>
       </c>
@@ -2976,7 +2978,7 @@
       <c r="AF13" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AG13" s="83"/>
+      <c r="AG13" s="88"/>
       <c r="AH13" s="6">
         <v>3</v>
       </c>
@@ -2988,20 +2990,22 @@
       </c>
       <c r="AK13" s="51"/>
       <c r="AL13" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM13" s="51" t="s">
         <v>176</v>
-      </c>
-      <c r="AM13" s="51" t="s">
-        <v>177</v>
       </c>
       <c r="AN13" s="51"/>
       <c r="AO13" s="51" t="s">
         <v>153</v>
       </c>
       <c r="AP13" s="51"/>
-      <c r="AR13" s="51"/>
+      <c r="AR13" s="51" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="14" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83"/>
+      <c r="A14" s="88"/>
       <c r="B14" s="6">
         <v>4</v>
       </c>
@@ -3029,7 +3033,7 @@
       <c r="J14" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="83"/>
+      <c r="K14" s="88"/>
       <c r="L14" s="6">
         <v>4</v>
       </c>
@@ -3057,7 +3061,7 @@
       <c r="T14" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="83"/>
+      <c r="U14" s="88"/>
       <c r="V14" s="6">
         <v>4</v>
       </c>
@@ -3091,7 +3095,7 @@
       <c r="AF14" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="AG14" s="83"/>
+      <c r="AG14" s="88"/>
       <c r="AH14" s="6">
         <v>4</v>
       </c>
@@ -3105,17 +3109,15 @@
       <c r="AL14" s="51"/>
       <c r="AM14" s="51"/>
       <c r="AN14" s="51" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AO14" s="51"/>
       <c r="AP14" s="51"/>
       <c r="AQ14" s="51"/>
-      <c r="AR14" s="51" t="s">
-        <v>153</v>
-      </c>
+      <c r="AR14" s="51"/>
     </row>
     <row r="15" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
+      <c r="A15" s="89"/>
       <c r="B15" s="7">
         <v>5</v>
       </c>
@@ -3127,7 +3129,7 @@
       <c r="H15" s="72"/>
       <c r="I15" s="72"/>
       <c r="J15" s="72"/>
-      <c r="K15" s="84"/>
+      <c r="K15" s="89"/>
       <c r="L15" s="7">
         <v>5</v>
       </c>
@@ -3139,7 +3141,7 @@
       <c r="R15" s="72"/>
       <c r="S15" s="72"/>
       <c r="T15" s="72"/>
-      <c r="U15" s="84"/>
+      <c r="U15" s="89"/>
       <c r="V15" s="7">
         <v>5</v>
       </c>
@@ -3159,7 +3161,7 @@
       <c r="AD15" s="72"/>
       <c r="AE15" s="72"/>
       <c r="AF15" s="72"/>
-      <c r="AG15" s="84"/>
+      <c r="AG15" s="89"/>
       <c r="AH15" s="7">
         <v>5</v>
       </c>
@@ -3175,7 +3177,7 @@
       <c r="AR15" s="52"/>
     </row>
     <row r="16" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="82">
+      <c r="A16" s="87">
         <v>4</v>
       </c>
       <c r="B16" s="4">
@@ -3194,10 +3196,10 @@
         <v>161</v>
       </c>
       <c r="G16" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H16" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I16" s="72" t="s">
         <v>104</v>
@@ -3205,7 +3207,7 @@
       <c r="J16" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="82">
+      <c r="K16" s="87">
         <v>4</v>
       </c>
       <c r="L16" s="4">
@@ -3235,7 +3237,7 @@
       <c r="T16" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="U16" s="82">
+      <c r="U16" s="87">
         <v>4</v>
       </c>
       <c r="V16" s="4">
@@ -3271,7 +3273,7 @@
       <c r="AF16" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="AG16" s="82">
+      <c r="AG16" s="87">
         <v>4</v>
       </c>
       <c r="AH16" s="4">
@@ -3295,7 +3297,7 @@
       <c r="AR16" s="52"/>
     </row>
     <row r="17" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="6">
         <v>2</v>
       </c>
@@ -3303,7 +3305,7 @@
         <v>56</v>
       </c>
       <c r="D17" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E17" s="72" t="s">
         <v>11</v>
@@ -3323,7 +3325,7 @@
       <c r="J17" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="K17" s="83"/>
+      <c r="K17" s="88"/>
       <c r="L17" s="6">
         <v>2</v>
       </c>
@@ -3346,12 +3348,12 @@
         <v>160</v>
       </c>
       <c r="S17" s="72" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="T17" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="U17" s="83"/>
+      <c r="U17" s="88"/>
       <c r="V17" s="6">
         <v>2</v>
       </c>
@@ -3380,17 +3382,17 @@
         <v>98</v>
       </c>
       <c r="AE17" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AF17" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="AG17" s="83"/>
+      <c r="AG17" s="88"/>
       <c r="AH17" s="6">
         <v>2</v>
       </c>
       <c r="AI17" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AJ17" s="72" t="s">
         <v>140</v>
@@ -3409,7 +3411,7 @@
       <c r="AR17" s="51"/>
     </row>
     <row r="18" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83"/>
+      <c r="A18" s="88"/>
       <c r="B18" s="6">
         <v>3</v>
       </c>
@@ -3437,15 +3439,15 @@
       <c r="J18" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="K18" s="83"/>
+      <c r="K18" s="88"/>
       <c r="L18" s="6">
         <v>3</v>
       </c>
       <c r="M18" s="72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N18" s="72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O18" s="72" t="s">
         <v>159</v>
@@ -3465,7 +3467,7 @@
       <c r="T18" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="U18" s="83"/>
+      <c r="U18" s="88"/>
       <c r="V18" s="6">
         <v>3</v>
       </c>
@@ -3499,7 +3501,7 @@
       <c r="AF18" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AG18" s="83"/>
+      <c r="AG18" s="88"/>
       <c r="AH18" s="6">
         <v>3</v>
       </c>
@@ -3523,12 +3525,12 @@
       <c r="AR18" s="51"/>
     </row>
     <row r="19" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83"/>
+      <c r="A19" s="88"/>
       <c r="B19" s="6">
         <v>4</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D19" s="72" t="s">
         <v>75</v>
@@ -3551,7 +3553,7 @@
       <c r="J19" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="K19" s="83"/>
+      <c r="K19" s="88"/>
       <c r="L19" s="6">
         <v>4</v>
       </c>
@@ -3579,7 +3581,7 @@
       <c r="T19" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="U19" s="83"/>
+      <c r="U19" s="88"/>
       <c r="V19" s="6">
         <v>4</v>
       </c>
@@ -3602,7 +3604,7 @@
         <v>127</v>
       </c>
       <c r="AC19" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AD19" s="72" t="s">
         <v>64</v>
@@ -3613,7 +3615,7 @@
       <c r="AF19" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="AG19" s="83"/>
+      <c r="AG19" s="88"/>
       <c r="AH19" s="6">
         <v>4</v>
       </c>
@@ -3626,20 +3628,16 @@
       <c r="AK19" s="51"/>
       <c r="AL19" s="51"/>
       <c r="AM19" s="51"/>
-      <c r="AN19" s="51" t="s">
-        <v>153</v>
-      </c>
+      <c r="AN19" s="51"/>
       <c r="AO19" s="51"/>
       <c r="AP19" s="51"/>
-      <c r="AQ19" s="51" t="s">
-        <v>153</v>
-      </c>
+      <c r="AQ19" s="51"/>
       <c r="AR19" s="51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="84"/>
+      <c r="A20" s="89"/>
       <c r="B20" s="7">
         <v>5</v>
       </c>
@@ -3651,7 +3649,7 @@
       <c r="H20" s="72"/>
       <c r="I20" s="72"/>
       <c r="J20" s="72"/>
-      <c r="K20" s="84"/>
+      <c r="K20" s="89"/>
       <c r="L20" s="7">
         <v>5</v>
       </c>
@@ -3663,7 +3661,7 @@
       <c r="R20" s="72"/>
       <c r="S20" s="72"/>
       <c r="T20" s="72"/>
-      <c r="U20" s="84"/>
+      <c r="U20" s="89"/>
       <c r="V20" s="7">
         <v>5</v>
       </c>
@@ -3683,7 +3681,7 @@
       <c r="AD20" s="72"/>
       <c r="AE20" s="72"/>
       <c r="AF20" s="72"/>
-      <c r="AG20" s="84"/>
+      <c r="AG20" s="89"/>
       <c r="AH20" s="7">
         <v>5</v>
       </c>
@@ -3699,17 +3697,17 @@
       <c r="AR20" s="52"/>
     </row>
     <row r="21" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="82">
+      <c r="A21" s="87">
         <v>5</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D21" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E21" s="72" t="s">
         <v>98</v>
@@ -3729,7 +3727,7 @@
       <c r="J21" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="K21" s="82">
+      <c r="K21" s="87">
         <v>5</v>
       </c>
       <c r="L21" s="4">
@@ -3759,7 +3757,7 @@
       <c r="T21" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="U21" s="82">
+      <c r="U21" s="87">
         <v>5</v>
       </c>
       <c r="V21" s="4">
@@ -3795,7 +3793,7 @@
       <c r="AF21" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="AG21" s="82">
+      <c r="AG21" s="87">
         <v>5</v>
       </c>
       <c r="AH21" s="4">
@@ -3819,7 +3817,7 @@
       <c r="AR21" s="52"/>
     </row>
     <row r="22" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83"/>
+      <c r="A22" s="88"/>
       <c r="B22" s="6">
         <v>2</v>
       </c>
@@ -3836,7 +3834,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H22" s="72" t="s">
         <v>100</v>
@@ -3847,7 +3845,7 @@
       <c r="J22" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="K22" s="83"/>
+      <c r="K22" s="88"/>
       <c r="L22" s="6">
         <v>2</v>
       </c>
@@ -3875,7 +3873,7 @@
       <c r="T22" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="U22" s="83"/>
+      <c r="U22" s="88"/>
       <c r="V22" s="6">
         <v>2</v>
       </c>
@@ -3909,7 +3907,7 @@
       <c r="AF22" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AG22" s="83"/>
+      <c r="AG22" s="88"/>
       <c r="AH22" s="6">
         <v>2</v>
       </c>
@@ -3929,13 +3927,13 @@
       </c>
       <c r="AO22" s="51"/>
       <c r="AP22" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AQ22" s="51"/>
       <c r="AR22" s="51"/>
     </row>
     <row r="23" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="83"/>
+      <c r="A23" s="88"/>
       <c r="B23" s="6">
         <v>3</v>
       </c>
@@ -3963,15 +3961,15 @@
       <c r="J23" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="K23" s="83"/>
+      <c r="K23" s="88"/>
       <c r="L23" s="6">
         <v>3</v>
       </c>
       <c r="M23" s="72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N23" s="72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O23" s="72" t="s">
         <v>10</v>
@@ -3991,7 +3989,7 @@
       <c r="T23" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="U23" s="83"/>
+      <c r="U23" s="88"/>
       <c r="V23" s="6">
         <v>3</v>
       </c>
@@ -4025,7 +4023,7 @@
       <c r="AF23" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="AG23" s="83"/>
+      <c r="AG23" s="88"/>
       <c r="AH23" s="6">
         <v>3</v>
       </c>
@@ -4035,9 +4033,7 @@
       <c r="AJ23" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="AK23" s="51" t="s">
-        <v>153</v>
-      </c>
+      <c r="AK23" s="51"/>
       <c r="AL23" s="51" t="s">
         <v>153</v>
       </c>
@@ -4045,11 +4041,13 @@
       <c r="AN23" s="51"/>
       <c r="AO23" s="51"/>
       <c r="AP23" s="51"/>
-      <c r="AQ23" s="51"/>
+      <c r="AQ23" s="51" t="s">
+        <v>153</v>
+      </c>
       <c r="AR23" s="51"/>
     </row>
     <row r="24" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="83"/>
+      <c r="A24" s="88"/>
       <c r="B24" s="6">
         <v>4</v>
       </c>
@@ -4066,7 +4064,7 @@
         <v>114</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H24" s="72" t="s">
         <v>102</v>
@@ -4077,7 +4075,7 @@
       <c r="J24" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="K24" s="83"/>
+      <c r="K24" s="88"/>
       <c r="L24" s="6">
         <v>4</v>
       </c>
@@ -4105,7 +4103,7 @@
       <c r="T24" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="U24" s="83"/>
+      <c r="U24" s="88"/>
       <c r="V24" s="6">
         <v>4</v>
       </c>
@@ -4131,7 +4129,7 @@
         <v>98</v>
       </c>
       <c r="AD24" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AE24" s="72" t="s">
         <v>145</v>
@@ -4139,7 +4137,7 @@
       <c r="AF24" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="AG24" s="83"/>
+      <c r="AG24" s="88"/>
       <c r="AH24" s="6">
         <v>4</v>
       </c>
@@ -4161,7 +4159,7 @@
       </c>
     </row>
     <row r="25" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="89"/>
       <c r="B25" s="7">
         <v>5</v>
       </c>
@@ -4173,7 +4171,7 @@
       <c r="H25" s="72"/>
       <c r="I25" s="72"/>
       <c r="J25" s="72"/>
-      <c r="K25" s="84"/>
+      <c r="K25" s="89"/>
       <c r="L25" s="7">
         <v>5</v>
       </c>
@@ -4185,7 +4183,7 @@
       <c r="R25" s="72"/>
       <c r="S25" s="72"/>
       <c r="T25" s="72"/>
-      <c r="U25" s="84"/>
+      <c r="U25" s="89"/>
       <c r="V25" s="7">
         <v>5</v>
       </c>
@@ -4205,7 +4203,7 @@
       <c r="AD25" s="72"/>
       <c r="AE25" s="72"/>
       <c r="AF25" s="72"/>
-      <c r="AG25" s="84"/>
+      <c r="AG25" s="89"/>
       <c r="AH25" s="7">
         <v>5</v>
       </c>
@@ -4221,10 +4219,10 @@
       <c r="AR25" s="52"/>
     </row>
     <row r="26" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="122">
+      <c r="A26" s="90">
         <v>6</v>
       </c>
-      <c r="B26" s="123">
+      <c r="B26" s="77">
         <v>1</v>
       </c>
       <c r="C26" s="72" t="s">
@@ -4251,10 +4249,10 @@
       <c r="J26" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="K26" s="122">
+      <c r="K26" s="90">
         <v>6</v>
       </c>
-      <c r="L26" s="123">
+      <c r="L26" s="77">
         <v>1</v>
       </c>
       <c r="M26" s="72" t="s">
@@ -4281,10 +4279,10 @@
       <c r="T26" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="U26" s="122">
+      <c r="U26" s="90">
         <v>6</v>
       </c>
-      <c r="V26" s="123">
+      <c r="V26" s="77">
         <v>1</v>
       </c>
       <c r="W26" s="72" t="s">
@@ -4306,7 +4304,7 @@
         <v>112</v>
       </c>
       <c r="AC26" s="72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AD26" s="72" t="s">
         <v>24</v>
@@ -4317,10 +4315,10 @@
       <c r="AF26" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="AG26" s="122">
+      <c r="AG26" s="90">
         <v>6</v>
       </c>
-      <c r="AH26" s="123">
+      <c r="AH26" s="77">
         <v>1</v>
       </c>
       <c r="AI26" s="72" t="s">
@@ -4341,8 +4339,8 @@
       <c r="AR26" s="52"/>
     </row>
     <row r="27" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="122"/>
-      <c r="B27" s="123">
+      <c r="A27" s="90"/>
+      <c r="B27" s="77">
         <v>2</v>
       </c>
       <c r="C27" s="72" t="s">
@@ -4369,8 +4367,8 @@
       <c r="J27" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="K27" s="122"/>
-      <c r="L27" s="123">
+      <c r="K27" s="90"/>
+      <c r="L27" s="77">
         <v>2</v>
       </c>
       <c r="M27" s="72" t="s">
@@ -4397,8 +4395,8 @@
       <c r="T27" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="U27" s="122"/>
-      <c r="V27" s="123">
+      <c r="U27" s="90"/>
+      <c r="V27" s="77">
         <v>2</v>
       </c>
       <c r="W27" s="72" t="s">
@@ -4431,8 +4429,8 @@
       <c r="AF27" s="72" t="s">
         <v>144</v>
       </c>
-      <c r="AG27" s="122"/>
-      <c r="AH27" s="123">
+      <c r="AG27" s="90"/>
+      <c r="AH27" s="77">
         <v>2</v>
       </c>
       <c r="AI27" s="72" t="s">
@@ -4442,7 +4440,7 @@
         <v>151</v>
       </c>
       <c r="AK27" s="51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AL27" s="51"/>
       <c r="AM27" s="51"/>
@@ -4455,12 +4453,12 @@
       <c r="AP27" s="51"/>
       <c r="AQ27" s="51"/>
       <c r="AR27" s="51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="122"/>
-      <c r="B28" s="123">
+      <c r="A28" s="90"/>
+      <c r="B28" s="77">
         <v>3</v>
       </c>
       <c r="C28" s="72" t="s">
@@ -4487,8 +4485,8 @@
       <c r="J28" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="K28" s="122"/>
-      <c r="L28" s="123">
+      <c r="K28" s="90"/>
+      <c r="L28" s="77">
         <v>3</v>
       </c>
       <c r="M28" s="72" t="s">
@@ -4515,8 +4513,8 @@
       <c r="T28" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="U28" s="122"/>
-      <c r="V28" s="123">
+      <c r="U28" s="90"/>
+      <c r="V28" s="77">
         <v>3</v>
       </c>
       <c r="W28" s="72" t="s">
@@ -4541,7 +4539,7 @@
         <v>108</v>
       </c>
       <c r="AD28" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AE28" s="72" t="s">
         <v>134</v>
@@ -4549,8 +4547,8 @@
       <c r="AF28" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="AG28" s="122"/>
-      <c r="AH28" s="123">
+      <c r="AG28" s="90"/>
+      <c r="AH28" s="77">
         <v>3</v>
       </c>
       <c r="AI28" s="72" t="s">
@@ -4559,22 +4557,24 @@
       <c r="AJ28" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="AK28" s="51"/>
-      <c r="AL28" s="51" t="s">
+      <c r="AK28" s="51" t="s">
         <v>153</v>
       </c>
+      <c r="AL28" s="51"/>
       <c r="AM28" s="51" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN28" s="51"/>
       <c r="AO28" s="51"/>
       <c r="AP28" s="51"/>
       <c r="AQ28" s="51"/>
-      <c r="AR28" s="51"/>
+      <c r="AR28" s="51" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="29" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="122"/>
-      <c r="B29" s="123">
+      <c r="A29" s="90"/>
+      <c r="B29" s="77">
         <v>4</v>
       </c>
       <c r="C29" s="72" t="s">
@@ -4601,8 +4601,8 @@
       <c r="J29" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="K29" s="122"/>
-      <c r="L29" s="123">
+      <c r="K29" s="90"/>
+      <c r="L29" s="77">
         <v>4</v>
       </c>
       <c r="M29" s="72" t="s">
@@ -4629,8 +4629,8 @@
       <c r="T29" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="U29" s="122"/>
-      <c r="V29" s="123">
+      <c r="U29" s="90"/>
+      <c r="V29" s="77">
         <v>4</v>
       </c>
       <c r="W29" s="72" t="s">
@@ -4658,20 +4658,20 @@
         <v>20</v>
       </c>
       <c r="AE29" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AF29" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="AG29" s="122"/>
-      <c r="AH29" s="123">
+        <v>172</v>
+      </c>
+      <c r="AG29" s="90"/>
+      <c r="AH29" s="77">
         <v>4</v>
       </c>
       <c r="AI29" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AJ29" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AK29" s="52"/>
       <c r="AL29" s="51"/>
@@ -4680,13 +4680,11 @@
       <c r="AO29" s="52"/>
       <c r="AP29" s="51"/>
       <c r="AQ29" s="51"/>
-      <c r="AR29" s="51" t="s">
-        <v>153</v>
-      </c>
+      <c r="AR29" s="51"/>
     </row>
     <row r="30" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="122"/>
-      <c r="B30" s="123">
+      <c r="A30" s="90"/>
+      <c r="B30" s="77">
         <v>5</v>
       </c>
       <c r="C30" s="72"/>
@@ -4697,8 +4695,8 @@
       <c r="H30" s="72"/>
       <c r="I30" s="72"/>
       <c r="J30" s="72"/>
-      <c r="K30" s="122"/>
-      <c r="L30" s="123">
+      <c r="K30" s="90"/>
+      <c r="L30" s="77">
         <v>5</v>
       </c>
       <c r="M30" s="72"/>
@@ -4709,8 +4707,8 @@
       <c r="R30" s="72"/>
       <c r="S30" s="72"/>
       <c r="T30" s="72"/>
-      <c r="U30" s="122"/>
-      <c r="V30" s="123">
+      <c r="U30" s="90"/>
+      <c r="V30" s="77">
         <v>5</v>
       </c>
       <c r="W30" s="72" t="s">
@@ -4729,8 +4727,8 @@
       <c r="AD30" s="73"/>
       <c r="AE30" s="73"/>
       <c r="AF30" s="73"/>
-      <c r="AG30" s="122"/>
-      <c r="AH30" s="123">
+      <c r="AG30" s="90"/>
+      <c r="AH30" s="77">
         <v>5</v>
       </c>
       <c r="AI30" s="72"/>
@@ -4745,299 +4743,280 @@
       <c r="AR30" s="52"/>
     </row>
     <row r="31" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="118"/>
-      <c r="B31" s="119"/>
-      <c r="C31" s="120"/>
-      <c r="D31" s="124"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="125"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="125"/>
-      <c r="I31" s="124"/>
-      <c r="J31" s="124"/>
-      <c r="K31" s="125"/>
-      <c r="L31" s="125"/>
-      <c r="M31" s="120"/>
-      <c r="N31" s="120"/>
-      <c r="O31" s="120"/>
-      <c r="P31" s="120"/>
-      <c r="Q31" s="120"/>
-      <c r="R31" s="120"/>
-      <c r="S31" s="120"/>
-      <c r="T31" s="120"/>
-      <c r="U31" s="120"/>
-      <c r="V31" s="120"/>
-      <c r="W31" s="120"/>
-      <c r="X31" s="120"/>
-      <c r="Y31" s="120"/>
-      <c r="Z31" s="120"/>
-      <c r="AA31" s="120"/>
-      <c r="AB31" s="120"/>
-      <c r="AC31" s="120"/>
-      <c r="AD31" s="121"/>
-      <c r="AE31" s="121"/>
-      <c r="AF31" s="121"/>
-      <c r="AG31" s="121"/>
-      <c r="AH31" s="121"/>
-      <c r="AI31" s="120"/>
-      <c r="AJ31" s="120"/>
-      <c r="AK31" s="120"/>
-      <c r="AL31" s="120"/>
-      <c r="AM31" s="120"/>
-      <c r="AN31" s="120"/>
-      <c r="AO31" s="120"/>
-      <c r="AP31" s="121"/>
-      <c r="AQ31" s="121"/>
-      <c r="AR31" s="121"/>
+      <c r="A31" s="93"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="78"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="75"/>
+      <c r="Q31" s="75"/>
+      <c r="R31" s="75"/>
+      <c r="S31" s="75"/>
+      <c r="T31" s="75"/>
+      <c r="U31" s="75"/>
+      <c r="V31" s="75"/>
+      <c r="W31" s="75"/>
+      <c r="X31" s="75"/>
+      <c r="Y31" s="75"/>
+      <c r="Z31" s="75"/>
+      <c r="AA31" s="75"/>
+      <c r="AB31" s="75"/>
+      <c r="AC31" s="75"/>
+      <c r="AD31" s="76"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="76"/>
+      <c r="AG31" s="76"/>
+      <c r="AH31" s="76"/>
+      <c r="AI31" s="75"/>
+      <c r="AJ31" s="75"/>
+      <c r="AK31" s="75"/>
+      <c r="AL31" s="75"/>
+      <c r="AM31" s="75"/>
+      <c r="AN31" s="75"/>
+      <c r="AO31" s="75"/>
+      <c r="AP31" s="76"/>
+      <c r="AQ31" s="76"/>
+      <c r="AR31" s="76"/>
     </row>
     <row r="32" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="118"/>
-      <c r="B32" s="119"/>
-      <c r="C32" s="120"/>
-      <c r="D32" s="124" t="s">
-        <v>183</v>
-      </c>
-      <c r="E32" s="124"/>
-      <c r="F32" s="125"/>
-      <c r="G32" s="125"/>
-      <c r="H32" s="125"/>
-      <c r="I32" s="124" t="s">
+      <c r="A32" s="93"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="81"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="J32" s="81"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="75"/>
+      <c r="N32" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="O32" s="81"/>
+      <c r="P32" s="78"/>
+      <c r="Q32" s="78"/>
+      <c r="R32" s="78"/>
+      <c r="S32" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="T32" s="81"/>
+      <c r="U32" s="78"/>
+      <c r="V32" s="78"/>
+      <c r="W32" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="X32" s="81"/>
+      <c r="Y32" s="78"/>
+      <c r="Z32" s="78"/>
+      <c r="AA32" s="78"/>
+      <c r="AB32" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC32" s="81"/>
+      <c r="AD32" s="76"/>
+      <c r="AE32" s="76"/>
+      <c r="AF32" s="76"/>
+      <c r="AG32" s="76"/>
+      <c r="AH32" s="76"/>
+      <c r="AI32" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="AJ32" s="81"/>
+      <c r="AK32" s="78"/>
+      <c r="AL32" s="78"/>
+      <c r="AM32" s="78"/>
+      <c r="AN32" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="AO32" s="81"/>
+      <c r="AP32" s="76"/>
+      <c r="AQ32" s="76"/>
+      <c r="AR32" s="76"/>
+    </row>
+    <row r="33" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="93"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="75"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
+      <c r="P33" s="79"/>
+      <c r="Q33" s="79"/>
+      <c r="R33" s="79"/>
+      <c r="S33" s="79"/>
+      <c r="T33" s="79"/>
+      <c r="U33" s="79"/>
+      <c r="V33" s="79"/>
+      <c r="W33" s="79"/>
+      <c r="X33" s="79"/>
+      <c r="Y33" s="79"/>
+      <c r="Z33" s="79"/>
+      <c r="AA33" s="79"/>
+      <c r="AB33" s="79"/>
+      <c r="AC33" s="79"/>
+      <c r="AD33" s="76"/>
+      <c r="AE33" s="76"/>
+      <c r="AF33" s="76"/>
+      <c r="AG33" s="76"/>
+      <c r="AH33" s="76"/>
+      <c r="AI33" s="79"/>
+      <c r="AJ33" s="79"/>
+      <c r="AK33" s="79"/>
+      <c r="AL33" s="79"/>
+      <c r="AM33" s="79"/>
+      <c r="AN33" s="79"/>
+      <c r="AO33" s="79"/>
+      <c r="AP33" s="76"/>
+      <c r="AQ33" s="76"/>
+      <c r="AR33" s="76"/>
+    </row>
+    <row r="34" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="93"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="78"/>
+      <c r="L34" s="78"/>
+      <c r="M34" s="75"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="79"/>
+      <c r="P34" s="79"/>
+      <c r="Q34" s="79"/>
+      <c r="R34" s="79"/>
+      <c r="S34" s="79"/>
+      <c r="T34" s="79"/>
+      <c r="U34" s="79"/>
+      <c r="V34" s="79"/>
+      <c r="W34" s="79"/>
+      <c r="X34" s="79"/>
+      <c r="Y34" s="79"/>
+      <c r="Z34" s="79"/>
+      <c r="AA34" s="79"/>
+      <c r="AB34" s="79"/>
+      <c r="AC34" s="79"/>
+      <c r="AD34" s="76"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="76"/>
+      <c r="AG34" s="76"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="79"/>
+      <c r="AJ34" s="79"/>
+      <c r="AK34" s="79"/>
+      <c r="AL34" s="79"/>
+      <c r="AM34" s="79"/>
+      <c r="AN34" s="79"/>
+      <c r="AO34" s="79"/>
+      <c r="AP34" s="76"/>
+      <c r="AQ34" s="76"/>
+      <c r="AR34" s="76"/>
+    </row>
+    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="D35" s="81" t="s">
         <v>180</v>
       </c>
-      <c r="J32" s="124"/>
-      <c r="K32" s="126"/>
-      <c r="L32" s="126"/>
-      <c r="M32" s="120"/>
-      <c r="N32" s="124" t="s">
-        <v>183</v>
-      </c>
-      <c r="O32" s="124"/>
-      <c r="P32" s="125"/>
-      <c r="Q32" s="125"/>
-      <c r="R32" s="125"/>
-      <c r="S32" s="124" t="s">
+      <c r="E35" s="81"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="J35" s="81"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="80"/>
+      <c r="N35" s="81" t="s">
         <v>180</v>
       </c>
-      <c r="T32" s="124"/>
-      <c r="U32" s="125"/>
-      <c r="V32" s="125"/>
-      <c r="W32" s="124" t="s">
-        <v>183</v>
-      </c>
-      <c r="X32" s="124"/>
-      <c r="Y32" s="125"/>
-      <c r="Z32" s="125"/>
-      <c r="AA32" s="125"/>
-      <c r="AB32" s="124" t="s">
+      <c r="O35" s="81"/>
+      <c r="P35" s="78"/>
+      <c r="Q35" s="78"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="T35" s="81"/>
+      <c r="U35" s="78"/>
+      <c r="V35" s="78"/>
+      <c r="W35" s="81" t="s">
         <v>180</v>
       </c>
-      <c r="AC32" s="124"/>
-      <c r="AD32" s="121"/>
-      <c r="AE32" s="121"/>
-      <c r="AF32" s="121"/>
-      <c r="AG32" s="121"/>
-      <c r="AH32" s="121"/>
-      <c r="AI32" s="124" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ32" s="124"/>
-      <c r="AK32" s="125"/>
-      <c r="AL32" s="125"/>
-      <c r="AM32" s="125"/>
-      <c r="AN32" s="124" t="s">
+      <c r="X35" s="81"/>
+      <c r="Y35" s="78"/>
+      <c r="Z35" s="78"/>
+      <c r="AA35" s="78"/>
+      <c r="AB35" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC35" s="81"/>
+      <c r="AI35" s="81" t="s">
         <v>180</v>
       </c>
-      <c r="AO32" s="124"/>
-      <c r="AP32" s="121"/>
-      <c r="AQ32" s="121"/>
-      <c r="AR32" s="121"/>
-    </row>
-    <row r="33" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="118"/>
-      <c r="B33" s="119"/>
-      <c r="C33" s="120"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="126"/>
-      <c r="F33" s="126"/>
-      <c r="G33" s="126"/>
-      <c r="H33" s="126"/>
-      <c r="I33" s="126"/>
-      <c r="J33" s="126"/>
-      <c r="K33" s="126"/>
-      <c r="L33" s="126"/>
-      <c r="M33" s="120"/>
-      <c r="N33" s="126"/>
-      <c r="O33" s="126"/>
-      <c r="P33" s="126"/>
-      <c r="Q33" s="126"/>
-      <c r="R33" s="126"/>
-      <c r="S33" s="126"/>
-      <c r="T33" s="126"/>
-      <c r="U33" s="126"/>
-      <c r="V33" s="126"/>
-      <c r="W33" s="126"/>
-      <c r="X33" s="126"/>
-      <c r="Y33" s="126"/>
-      <c r="Z33" s="126"/>
-      <c r="AA33" s="126"/>
-      <c r="AB33" s="126"/>
-      <c r="AC33" s="126"/>
-      <c r="AD33" s="121"/>
-      <c r="AE33" s="121"/>
-      <c r="AF33" s="121"/>
-      <c r="AG33" s="121"/>
-      <c r="AH33" s="121"/>
-      <c r="AI33" s="126"/>
-      <c r="AJ33" s="126"/>
-      <c r="AK33" s="126"/>
-      <c r="AL33" s="126"/>
-      <c r="AM33" s="126"/>
-      <c r="AN33" s="126"/>
-      <c r="AO33" s="126"/>
-      <c r="AP33" s="121"/>
-      <c r="AQ33" s="121"/>
-      <c r="AR33" s="121"/>
-    </row>
-    <row r="34" spans="1:44" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="118"/>
-      <c r="B34" s="119"/>
-      <c r="C34" s="120"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126"/>
-      <c r="G34" s="126"/>
-      <c r="H34" s="126"/>
-      <c r="I34" s="126"/>
-      <c r="J34" s="126"/>
-      <c r="K34" s="125"/>
-      <c r="L34" s="125"/>
-      <c r="M34" s="120"/>
-      <c r="N34" s="126"/>
-      <c r="O34" s="126"/>
-      <c r="P34" s="126"/>
-      <c r="Q34" s="126"/>
-      <c r="R34" s="126"/>
-      <c r="S34" s="126"/>
-      <c r="T34" s="126"/>
-      <c r="U34" s="126"/>
-      <c r="V34" s="126"/>
-      <c r="W34" s="126"/>
-      <c r="X34" s="126"/>
-      <c r="Y34" s="126"/>
-      <c r="Z34" s="126"/>
-      <c r="AA34" s="126"/>
-      <c r="AB34" s="126"/>
-      <c r="AC34" s="126"/>
-      <c r="AD34" s="121"/>
-      <c r="AE34" s="121"/>
-      <c r="AF34" s="121"/>
-      <c r="AG34" s="121"/>
-      <c r="AH34" s="121"/>
-      <c r="AI34" s="126"/>
-      <c r="AJ34" s="126"/>
-      <c r="AK34" s="126"/>
-      <c r="AL34" s="126"/>
-      <c r="AM34" s="126"/>
-      <c r="AN34" s="126"/>
-      <c r="AO34" s="126"/>
-      <c r="AP34" s="121"/>
-      <c r="AQ34" s="121"/>
-      <c r="AR34" s="121"/>
-    </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="D35" s="124" t="s">
+      <c r="AJ35" s="81"/>
+      <c r="AK35" s="78"/>
+      <c r="AL35" s="78"/>
+      <c r="AM35" s="78"/>
+      <c r="AN35" s="81" t="s">
         <v>181</v>
       </c>
-      <c r="E35" s="124"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="125"/>
-      <c r="I35" s="124" t="s">
-        <v>182</v>
-      </c>
-      <c r="J35" s="124"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="127"/>
-      <c r="N35" s="124" t="s">
-        <v>181</v>
-      </c>
-      <c r="O35" s="124"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="125"/>
-      <c r="S35" s="124" t="s">
-        <v>182</v>
-      </c>
-      <c r="T35" s="124"/>
-      <c r="U35" s="125"/>
-      <c r="V35" s="125"/>
-      <c r="W35" s="124" t="s">
-        <v>181</v>
-      </c>
-      <c r="X35" s="124"/>
-      <c r="Y35" s="125"/>
-      <c r="Z35" s="125"/>
-      <c r="AA35" s="125"/>
-      <c r="AB35" s="124" t="s">
-        <v>182</v>
-      </c>
-      <c r="AC35" s="124"/>
-      <c r="AI35" s="124" t="s">
-        <v>181</v>
-      </c>
-      <c r="AJ35" s="124"/>
-      <c r="AK35" s="125"/>
-      <c r="AL35" s="125"/>
-      <c r="AM35" s="125"/>
-      <c r="AN35" s="124" t="s">
-        <v>182</v>
-      </c>
-      <c r="AO35" s="124"/>
+      <c r="AO35" s="81"/>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="127"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="127"/>
-      <c r="J36" s="127"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="AI32:AJ32"/>
-    <mergeCell ref="AN32:AO32"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AN35:AO35"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AG21:AG25"/>
-    <mergeCell ref="AG26:AG30"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AH5"/>
-    <mergeCell ref="AG6:AG10"/>
-    <mergeCell ref="AG11:AG15"/>
-    <mergeCell ref="AG16:AG20"/>
-    <mergeCell ref="U6:U10"/>
-    <mergeCell ref="U11:U15"/>
-    <mergeCell ref="U16:U20"/>
-    <mergeCell ref="U21:U25"/>
-    <mergeCell ref="U26:U30"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="K11:K15"/>
-    <mergeCell ref="K16:K20"/>
     <mergeCell ref="K21:K25"/>
     <mergeCell ref="K26:K30"/>
     <mergeCell ref="AE4:AF4"/>
@@ -5054,18 +5033,37 @@
     <mergeCell ref="AC4:AD4"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AG6:AG10"/>
+    <mergeCell ref="AG11:AG15"/>
+    <mergeCell ref="AG16:AG20"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="U21:U25"/>
+    <mergeCell ref="U26:U30"/>
+    <mergeCell ref="AG21:AG25"/>
+    <mergeCell ref="AG26:AG30"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="K11:K15"/>
+    <mergeCell ref="K16:K20"/>
+    <mergeCell ref="U6:U10"/>
+    <mergeCell ref="U11:U15"/>
+    <mergeCell ref="U16:U20"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="AI32:AJ32"/>
+    <mergeCell ref="AN32:AO32"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AN35:AO35"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="S35:T35"/>
   </mergeCells>
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.4" right="0" top="0" bottom="0" header="0.5" footer="0.5"/>
@@ -5094,45 +5092,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="75" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="75"/>
-      <c r="Z1" s="75"/>
-      <c r="AA1" s="75"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="75"/>
-      <c r="AD1" s="75"/>
-      <c r="AE1" s="75"/>
-      <c r="AF1" s="75"/>
-      <c r="AG1" s="75"/>
-      <c r="AH1" s="75"/>
-      <c r="AI1" s="75"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="108"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -5141,41 +5139,41 @@
       <c r="BF1" s="1"/>
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
-      <c r="S2" s="90"/>
-      <c r="T2" s="90"/>
-      <c r="U2" s="90"/>
-      <c r="V2" s="90"/>
-      <c r="W2" s="90"/>
-      <c r="X2" s="90"/>
-      <c r="Y2" s="90"/>
-      <c r="Z2" s="90"/>
-      <c r="AA2" s="90"/>
-      <c r="AB2" s="90"/>
-      <c r="AC2" s="90"/>
-      <c r="AD2" s="90"/>
-      <c r="AE2" s="90"/>
-      <c r="AF2" s="90"/>
-      <c r="AG2" s="90"/>
-      <c r="AH2" s="90"/>
-      <c r="AI2" s="90"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="109"/>
+      <c r="S2" s="109"/>
+      <c r="T2" s="109"/>
+      <c r="U2" s="109"/>
+      <c r="V2" s="109"/>
+      <c r="W2" s="109"/>
+      <c r="X2" s="109"/>
+      <c r="Y2" s="109"/>
+      <c r="Z2" s="109"/>
+      <c r="AA2" s="109"/>
+      <c r="AB2" s="109"/>
+      <c r="AC2" s="109"/>
+      <c r="AD2" s="109"/>
+      <c r="AE2" s="109"/>
+      <c r="AF2" s="109"/>
+      <c r="AG2" s="109"/>
+      <c r="AH2" s="109"/>
+      <c r="AI2" s="109"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="3"/>
@@ -5236,100 +5234,100 @@
       <c r="BF3" s="2"/>
     </row>
     <row r="4" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="99" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="97" t="s">
+      <c r="B4" s="106" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="101" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="102"/>
+      <c r="E4" s="101" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="102"/>
+      <c r="G4" s="101" t="s">
+        <v>168</v>
+      </c>
+      <c r="H4" s="102"/>
+      <c r="I4" s="101" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="102"/>
+      <c r="K4" s="101" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="102"/>
+      <c r="M4" s="101" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="102"/>
+      <c r="O4" s="101" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="101" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="102"/>
+      <c r="S4" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="102"/>
+      <c r="U4" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="V4" s="102"/>
+      <c r="W4" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4" s="102"/>
+      <c r="Y4" s="101" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z4" s="102"/>
+      <c r="AA4" s="101" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB4" s="102"/>
+      <c r="AC4" s="101" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD4" s="102"/>
+      <c r="AE4" s="101" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF4" s="102"/>
+      <c r="AG4" s="101" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH4" s="102"/>
+      <c r="AI4" s="101" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ4" s="102"/>
+      <c r="AK4" s="101" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL4" s="102"/>
+      <c r="AM4" s="101" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN4" s="102"/>
+      <c r="AO4" s="101" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP4" s="102"/>
+      <c r="AQ4" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="98"/>
-      <c r="E4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="98"/>
-      <c r="G4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="H4" s="98"/>
-      <c r="I4" s="97" t="s">
+      <c r="AR4" s="102"/>
+      <c r="AS4" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="98"/>
-      <c r="M4" s="97" t="s">
-        <v>70</v>
-      </c>
-      <c r="N4" s="98"/>
-      <c r="O4" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="97" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" s="98"/>
-      <c r="S4" s="97" t="s">
-        <v>32</v>
-      </c>
-      <c r="T4" s="98"/>
-      <c r="U4" s="97" t="s">
-        <v>84</v>
-      </c>
-      <c r="V4" s="98"/>
-      <c r="W4" s="97" t="s">
-        <v>30</v>
-      </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="97" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="97" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="97" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD4" s="98"/>
-      <c r="AE4" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="97" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="AJ4" s="98"/>
-      <c r="AK4" s="97" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="97" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="97" t="s">
-        <v>33</v>
-      </c>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="97" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR4" s="98"/>
-      <c r="AS4" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="AT4" s="98"/>
+      <c r="AT4" s="102"/>
       <c r="AU4" s="69" t="s">
         <v>85</v>
       </c>
@@ -5370,26 +5368,26 @@
         <v>85</v>
       </c>
       <c r="BN4" s="70"/>
-      <c r="BO4" s="101" t="s">
+      <c r="BO4" s="99" t="s">
         <v>152</v>
       </c>
-      <c r="BP4" s="102"/>
-      <c r="BQ4" s="101" t="s">
+      <c r="BP4" s="100"/>
+      <c r="BQ4" s="99" t="s">
         <v>162</v>
       </c>
-      <c r="BR4" s="102"/>
-      <c r="BS4" s="101" t="s">
+      <c r="BR4" s="100"/>
+      <c r="BS4" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="BT4" s="102"/>
-      <c r="BU4" s="101" t="s">
+      <c r="BT4" s="100"/>
+      <c r="BU4" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="BV4" s="102"/>
+      <c r="BV4" s="100"/>
     </row>
     <row r="5" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="100"/>
-      <c r="B5" s="100"/>
+      <c r="A5" s="107"/>
+      <c r="B5" s="107"/>
       <c r="C5" s="37" t="s">
         <v>3</v>
       </c>
@@ -5608,7 +5606,7 @@
       </c>
     </row>
     <row r="6" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="91">
+      <c r="A6" s="110">
         <v>2</v>
       </c>
       <c r="B6" s="39">
@@ -5620,7 +5618,7 @@
       </c>
       <c r="D6" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B6&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -6A1</v>
       </c>
       <c r="E6" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B6&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -5628,7 +5626,7 @@
       </c>
       <c r="F6" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B6&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -2A1</v>
       </c>
       <c r="G6" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B6&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -5692,7 +5690,7 @@
       </c>
       <c r="V6" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B6&amp;$U$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GDĐP -6A1</v>
+        <v>Văn -7A1</v>
       </c>
       <c r="W6" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B6&amp;$W$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -5904,17 +5902,17 @@
       </c>
     </row>
     <row r="7" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="92"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="41">
         <v>2</v>
       </c>
       <c r="C7" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B7&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -6A1</v>
+        <v/>
       </c>
       <c r="D7" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B7&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -8A1</v>
       </c>
       <c r="E7" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B7&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -5922,7 +5920,7 @@
       </c>
       <c r="F7" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B7&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>Tiếng Trung -8A1</v>
+        <v>Tiếng Trung -3C1</v>
       </c>
       <c r="G7" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B7&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -5986,7 +5984,7 @@
       </c>
       <c r="V7" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B7&amp;$U$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>Văn -7A1</v>
+        <v/>
       </c>
       <c r="W7" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B7&amp;$W$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -6198,17 +6196,17 @@
       </c>
     </row>
     <row r="8" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="92"/>
+      <c r="A8" s="111"/>
       <c r="B8" s="41">
         <v>3</v>
       </c>
       <c r="C8" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B8&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -6A1</v>
+        <v/>
       </c>
       <c r="D8" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B8&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -7A1</v>
       </c>
       <c r="E8" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B8&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -6216,7 +6214,7 @@
       </c>
       <c r="F8" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B8&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>Tiếng Trung -7A1</v>
+        <v>Tiếng Trung -4C1</v>
       </c>
       <c r="G8" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B8&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -6492,13 +6490,13 @@
       </c>
     </row>
     <row r="9" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="92"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="41">
         <v>4</v>
       </c>
       <c r="C9" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B9&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -7A1</v>
+        <v/>
       </c>
       <c r="D9" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B9&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -6510,7 +6508,7 @@
       </c>
       <c r="F9" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B9&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>Tiếng Trung -6A1</v>
+        <v>Tiếng Trung -2C1</v>
       </c>
       <c r="G9" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B9&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -6574,7 +6572,7 @@
       </c>
       <c r="V9" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B9&amp;$U$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>GDĐP -6A1</v>
       </c>
       <c r="W9" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B9&amp;$W$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -6786,13 +6784,13 @@
       </c>
     </row>
     <row r="10" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="93"/>
+      <c r="A10" s="112"/>
       <c r="B10" s="42">
         <v>5</v>
       </c>
       <c r="C10" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$C$5&amp;$B10&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -7A1</v>
+        <v/>
       </c>
       <c r="D10" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$6&amp;$D$5&amp;$B10&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -7080,7 +7078,7 @@
       </c>
     </row>
     <row r="11" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="94">
+      <c r="A11" s="103">
         <v>3</v>
       </c>
       <c r="B11" s="39">
@@ -7088,11 +7086,11 @@
       </c>
       <c r="C11" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$C$5&amp;$B11&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -7A1</v>
+        <v/>
       </c>
       <c r="D11" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$D$5&amp;$B11&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -7A1</v>
+        <v/>
       </c>
       <c r="E11" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$C$5&amp;$B11&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -7376,7 +7374,7 @@
       </c>
     </row>
     <row r="12" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -7670,7 +7668,7 @@
       </c>
     </row>
     <row r="13" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="95"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -7682,9 +7680,7 @@
         <f>IFERROR(VLOOKUP($A$11&amp;$D$5&amp;$B13&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
         <v/>
       </c>
-      <c r="E13" s="40" t="s">
-        <v>166</v>
-      </c>
+      <c r="E13" s="40"/>
       <c r="F13" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$D$5&amp;$B13&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
         <v/>
@@ -7963,21 +7959,19 @@
       </c>
     </row>
     <row r="14" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="95"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="41">
         <v>4</v>
       </c>
       <c r="C14" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$C$5&amp;$B14&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -6A1</v>
+        <v/>
       </c>
       <c r="D14" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$D$5&amp;$B14&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
         <v/>
       </c>
-      <c r="E14" s="40" t="s">
-        <v>166</v>
-      </c>
+      <c r="E14" s="40"/>
       <c r="F14" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$D$5&amp;$B14&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
         <v/>
@@ -8256,13 +8250,13 @@
       </c>
     </row>
     <row r="15" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="96"/>
+      <c r="A15" s="105"/>
       <c r="B15" s="42">
         <v>5</v>
       </c>
       <c r="C15" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$C$5&amp;$B15&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -6A1</v>
+        <v/>
       </c>
       <c r="D15" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$11&amp;$D$5&amp;$B15&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -8550,7 +8544,7 @@
       </c>
     </row>
     <row r="16" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="94">
+      <c r="A16" s="103">
         <v>4</v>
       </c>
       <c r="B16" s="39">
@@ -8558,19 +8552,19 @@
       </c>
       <c r="C16" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B16&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -6A1</v>
       </c>
       <c r="D16" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B16&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -6A1</v>
+        <v/>
       </c>
       <c r="E16" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B16&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>Tiếng Trung -6A1</v>
+        <v/>
       </c>
       <c r="F16" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B16&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -3A1</v>
       </c>
       <c r="G16" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B16&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -8845,25 +8839,25 @@
       </c>
     </row>
     <row r="17" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="95"/>
+      <c r="A17" s="104"/>
       <c r="B17" s="41">
         <v>2</v>
       </c>
       <c r="C17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B17&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -6A1</v>
+        <v>Tiếng Trung -7A1</v>
       </c>
       <c r="D17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B17&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -6A1</v>
+        <v/>
       </c>
       <c r="E17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B17&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>Tiếng Trung -7A1</v>
+        <v/>
       </c>
       <c r="F17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B17&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -1C1</v>
       </c>
       <c r="G17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B17&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -8939,7 +8933,7 @@
       </c>
       <c r="Y17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B17&amp;$Y$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>TViệt -5C1</v>
       </c>
       <c r="Z17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B17&amp;$Y$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -8995,7 +8989,7 @@
       </c>
       <c r="AM17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B17&amp;$AM$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>TViệt -5C1</v>
+        <v/>
       </c>
       <c r="AN17" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B17&amp;$AM$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -9139,25 +9133,25 @@
       </c>
     </row>
     <row r="18" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="95"/>
+      <c r="A18" s="104"/>
       <c r="B18" s="41">
         <v>3</v>
       </c>
       <c r="C18" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B18&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -7A1</v>
+        <v>Tiếng Trung -8A1</v>
       </c>
       <c r="D18" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B18&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -7A1</v>
+        <v/>
       </c>
       <c r="E18" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B18&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>Tiếng Trung -8A1</v>
+        <v/>
       </c>
       <c r="F18" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B18&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -1A1</v>
       </c>
       <c r="G18" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B18&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -9433,7 +9427,7 @@
       </c>
     </row>
     <row r="19" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="95"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="41">
         <v>4</v>
       </c>
@@ -9451,7 +9445,7 @@
       </c>
       <c r="F19" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B19&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v/>
+        <v>Tiếng Trung -5C1</v>
       </c>
       <c r="G19" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B19&amp;$G$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -9727,13 +9721,13 @@
       </c>
     </row>
     <row r="20" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="96"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="42">
         <v>5</v>
       </c>
       <c r="C20" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$C$5&amp;$B20&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -7A1</v>
+        <v/>
       </c>
       <c r="D20" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$16&amp;$D$5&amp;$B20&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -10021,7 +10015,7 @@
       </c>
     </row>
     <row r="21" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="94">
+      <c r="A21" s="103">
         <v>5</v>
       </c>
       <c r="B21" s="39">
@@ -10029,11 +10023,11 @@
       </c>
       <c r="C21" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$C$5&amp;$B21&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -7A1</v>
+        <v/>
       </c>
       <c r="D21" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$D$5&amp;$B21&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -7A1</v>
+        <v/>
       </c>
       <c r="E21" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$C$5&amp;$B21&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -10317,7 +10311,7 @@
       </c>
     </row>
     <row r="22" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="95"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="41">
         <v>2</v>
       </c>
@@ -10327,7 +10321,7 @@
       </c>
       <c r="D22" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$D$5&amp;$B22&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVVN -6A1</v>
+        <v/>
       </c>
       <c r="E22" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$C$5&amp;$B22&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -10611,7 +10605,7 @@
       </c>
     </row>
     <row r="23" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="95"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="41">
         <v>3</v>
       </c>
@@ -10621,7 +10615,7 @@
       </c>
       <c r="D23" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$D$5&amp;$B23&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -6A1</v>
+        <v/>
       </c>
       <c r="E23" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$C$5&amp;$B23&amp;$E$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -10905,7 +10899,7 @@
       </c>
     </row>
     <row r="24" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="95"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="41">
         <v>4</v>
       </c>
@@ -11199,13 +11193,13 @@
       </c>
     </row>
     <row r="25" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="96"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="42">
         <v>5</v>
       </c>
       <c r="C25" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$C$5&amp;$B25&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
-        <v>GVNN -7A1</v>
+        <v/>
       </c>
       <c r="D25" s="40" t="str">
         <f>IFERROR(VLOOKUP($A$21&amp;$D$5&amp;$B25&amp;$C$4,TKB_LOP_CHECK!$B$65:$J$860,9,0),"")</f>
@@ -11493,7 +11487,7 @@
       </c>
     </row>
     <row r="26" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="94">
+      <c r="A26" s="103">
         <v>6</v>
       </c>
       <c r="B26" s="39">
@@ -11789,7 +11783,7 @@
       </c>
     </row>
     <row r="27" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="95"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="41">
         <v>2</v>
       </c>
@@ -12082,7 +12076,7 @@
       </c>
     </row>
     <row r="28" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="95"/>
+      <c r="A28" s="104"/>
       <c r="B28" s="41">
         <v>3</v>
       </c>
@@ -12376,7 +12370,7 @@
       </c>
     </row>
     <row r="29" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="95"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="41">
         <v>4</v>
       </c>
@@ -12670,7 +12664,7 @@
       </c>
     </row>
     <row r="30" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="96"/>
+      <c r="A30" s="105"/>
       <c r="B30" s="42">
         <v>5</v>
       </c>
@@ -12964,7 +12958,7 @@
       </c>
     </row>
     <row r="31" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="94">
+      <c r="A31" s="103">
         <v>7</v>
       </c>
       <c r="B31" s="39">
@@ -13044,7 +13038,7 @@
       <c r="BV31" s="45"/>
     </row>
     <row r="32" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="95"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="41">
         <v>2</v>
       </c>
@@ -13122,7 +13116,7 @@
       <c r="BV32" s="45"/>
     </row>
     <row r="33" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="95"/>
+      <c r="A33" s="104"/>
       <c r="B33" s="41">
         <v>3</v>
       </c>
@@ -13200,7 +13194,7 @@
       <c r="BV33" s="45"/>
     </row>
     <row r="34" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="95"/>
+      <c r="A34" s="104"/>
       <c r="B34" s="41">
         <v>4</v>
       </c>
@@ -13278,7 +13272,7 @@
       <c r="BV34" s="45"/>
     </row>
     <row r="35" spans="1:74" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="96"/>
+      <c r="A35" s="105"/>
       <c r="B35" s="42">
         <v>5</v>
       </c>
@@ -13358,28 +13352,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="37">
-    <mergeCell ref="BQ4:BR4"/>
-    <mergeCell ref="BS4:BT4"/>
-    <mergeCell ref="BU4:BV4"/>
-    <mergeCell ref="AM4:AN4"/>
-    <mergeCell ref="AO4:AP4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="AS4:AT4"/>
-    <mergeCell ref="BO4:BP4"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:AI1"/>
     <mergeCell ref="D2:AI2"/>
@@ -13395,6 +13367,28 @@
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="BQ4:BR4"/>
+    <mergeCell ref="BS4:BT4"/>
+    <mergeCell ref="BU4:BV4"/>
+    <mergeCell ref="AM4:AN4"/>
+    <mergeCell ref="AO4:AP4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="AS4:AT4"/>
+    <mergeCell ref="BO4:BP4"/>
   </mergeCells>
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.4" right="0" top="0" bottom="0" header="0.5" footer="0.5"/>
@@ -13432,57 +13426,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:131" ht="30" x14ac:dyDescent="0.25">
-      <c r="E1" s="104" t="s">
+      <c r="E1" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
       <c r="P1" s="28"/>
     </row>
     <row r="2" spans="5:131" x14ac:dyDescent="0.25">
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
       <c r="AB2" s="29" t="s">
         <v>79</v>
       </c>
       <c r="AU2" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="CG2" s="103" t="s">
+      <c r="CG2" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="CH2" s="103"/>
-      <c r="CI2" s="103"/>
-      <c r="DG2" s="103" t="s">
+      <c r="CH2" s="124"/>
+      <c r="CI2" s="124"/>
+      <c r="DG2" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="DH2" s="103"/>
-      <c r="DI2" s="103"/>
+      <c r="DH2" s="124"/>
+      <c r="DI2" s="124"/>
     </row>
     <row r="3" spans="5:131" ht="3.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E4" s="107" t="s">
+      <c r="E4" s="119" t="s">
         <v>0</v>
       </c>
       <c r="F4" s="23"/>
-      <c r="G4" s="107" t="s">
+      <c r="G4" s="119" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="25" t="s">
@@ -13539,11 +13533,11 @@
       <c r="Y4" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="Z4" s="107" t="s">
+      <c r="Z4" s="119" t="s">
         <v>0</v>
       </c>
       <c r="AA4" s="23"/>
-      <c r="AB4" s="107" t="s">
+      <c r="AB4" s="119" t="s">
         <v>1</v>
       </c>
       <c r="AC4" s="25" t="s">
@@ -13600,11 +13594,11 @@
       <c r="AT4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="AU4" s="107" t="s">
+      <c r="AU4" s="119" t="s">
         <v>0</v>
       </c>
       <c r="AV4" s="53"/>
-      <c r="AW4" s="107" t="s">
+      <c r="AW4" s="119" t="s">
         <v>1</v>
       </c>
       <c r="AX4" s="25" t="s">
@@ -13661,11 +13655,11 @@
       <c r="BO4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="BP4" s="107" t="s">
+      <c r="BP4" s="119" t="s">
         <v>0</v>
       </c>
       <c r="BQ4" s="53"/>
-      <c r="BR4" s="107" t="s">
+      <c r="BR4" s="119" t="s">
         <v>1</v>
       </c>
       <c r="BS4" s="25" t="s">
@@ -13707,11 +13701,11 @@
       <c r="CE4" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="CG4" s="107" t="s">
+      <c r="CG4" s="119" t="s">
         <v>0</v>
       </c>
       <c r="CH4" s="53"/>
-      <c r="CI4" s="107" t="s">
+      <c r="CI4" s="119" t="s">
         <v>1</v>
       </c>
       <c r="CJ4" s="25" t="s">
@@ -13768,11 +13762,11 @@
       <c r="DA4" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="DG4" s="107" t="s">
+      <c r="DG4" s="119" t="s">
         <v>0</v>
       </c>
       <c r="DH4" s="64"/>
-      <c r="DI4" s="107" t="s">
+      <c r="DI4" s="119" t="s">
         <v>1</v>
       </c>
       <c r="DJ4" s="25" t="s">
@@ -13831,9 +13825,9 @@
       </c>
     </row>
     <row r="5" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E5" s="108"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="24"/>
-      <c r="G5" s="108"/>
+      <c r="G5" s="120"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -13846,9 +13840,9 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
-      <c r="Z5" s="108"/>
+      <c r="Z5" s="120"/>
       <c r="AA5" s="24"/>
-      <c r="AB5" s="108"/>
+      <c r="AB5" s="120"/>
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
@@ -13867,9 +13861,9 @@
       <c r="AR5" s="57"/>
       <c r="AS5" s="57"/>
       <c r="AT5" s="57"/>
-      <c r="AU5" s="108"/>
+      <c r="AU5" s="120"/>
       <c r="AV5" s="54"/>
-      <c r="AW5" s="108"/>
+      <c r="AW5" s="120"/>
       <c r="AX5" s="8"/>
       <c r="AY5" s="8"/>
       <c r="AZ5" s="8"/>
@@ -13883,9 +13877,9 @@
       <c r="BH5" s="9"/>
       <c r="BI5" s="9"/>
       <c r="BJ5" s="57"/>
-      <c r="BP5" s="108"/>
+      <c r="BP5" s="120"/>
       <c r="BQ5" s="54"/>
-      <c r="BR5" s="108"/>
+      <c r="BR5" s="120"/>
       <c r="BS5" s="8"/>
       <c r="BT5" s="8"/>
       <c r="BU5" s="8"/>
@@ -13899,9 +13893,9 @@
       <c r="CC5" s="9"/>
       <c r="CD5" s="9"/>
       <c r="CE5" s="57"/>
-      <c r="CG5" s="108"/>
+      <c r="CG5" s="120"/>
       <c r="CH5" s="54"/>
-      <c r="CI5" s="108"/>
+      <c r="CI5" s="120"/>
       <c r="CJ5" s="8"/>
       <c r="CK5" s="8"/>
       <c r="CL5" s="8"/>
@@ -13920,9 +13914,9 @@
       <c r="CY5" s="9"/>
       <c r="CZ5" s="9"/>
       <c r="DA5" s="57"/>
-      <c r="DG5" s="108"/>
+      <c r="DG5" s="120"/>
       <c r="DH5" s="65"/>
-      <c r="DI5" s="108"/>
+      <c r="DI5" s="120"/>
       <c r="DJ5" s="8"/>
       <c r="DK5" s="8"/>
       <c r="DL5" s="8"/>
@@ -13938,10 +13932,10 @@
       <c r="DV5" s="57"/>
     </row>
     <row r="6" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="115">
+      <c r="E6" s="121">
         <v>2</v>
       </c>
-      <c r="F6" s="112" t="s">
+      <c r="F6" s="113" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="10">
@@ -14019,10 +14013,10 @@
         <f>TKB_LOP_SC!AQ6</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="115">
+      <c r="Z6" s="121">
         <v>2</v>
       </c>
-      <c r="AA6" s="112" t="s">
+      <c r="AA6" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AB6" s="10">
@@ -14100,10 +14094,10 @@
         <f t="shared" ref="AT6:AT60" si="15">IFERROR(LEFT(BS6,FIND(",",BS6)-1),"")</f>
         <v/>
       </c>
-      <c r="AU6" s="115">
+      <c r="AU6" s="121">
         <v>2</v>
       </c>
-      <c r="AV6" s="112" t="s">
+      <c r="AV6" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AW6" s="10">
@@ -14181,10 +14175,10 @@
         <f t="shared" ref="BO6:BO60" si="32">IFERROR(RIGHT(Y6,LEN(Y6)-FIND("-",Y6)-1),"")</f>
         <v/>
       </c>
-      <c r="BP6" s="115">
+      <c r="BP6" s="121">
         <v>2</v>
       </c>
-      <c r="BQ6" s="112" t="s">
+      <c r="BQ6" s="113" t="s">
         <v>3</v>
       </c>
       <c r="BR6" s="10">
@@ -14242,10 +14236,10 @@
         <f t="shared" ref="CE6:CE60" si="44">IFERROR(RIGHT(BJ6,LEN(BJ6)-FIND(",",BJ6)-1),BJ6)</f>
         <v>MN1</v>
       </c>
-      <c r="CG6" s="115">
+      <c r="CG6" s="121">
         <v>2</v>
       </c>
-      <c r="CH6" s="112" t="s">
+      <c r="CH6" s="113" t="s">
         <v>3</v>
       </c>
       <c r="CI6" s="10">
@@ -14323,10 +14317,10 @@
         <f t="shared" ref="DA6:DA60" si="61">IF(CJ6="","",COUNTIF($BS6:$CE6,CJ6))</f>
         <v>0</v>
       </c>
-      <c r="DG6" s="115">
+      <c r="DG6" s="121">
         <v>2</v>
       </c>
-      <c r="DH6" s="112" t="s">
+      <c r="DH6" s="113" t="s">
         <v>3</v>
       </c>
       <c r="DI6" s="10">
@@ -14406,8 +14400,8 @@
       </c>
     </row>
     <row r="7" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="116"/>
-      <c r="F7" s="113"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="114"/>
       <c r="G7" s="15">
         <v>2</v>
       </c>
@@ -14483,8 +14477,8 @@
         <f>TKB_LOP_SC!AQ7</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="116"/>
-      <c r="AA7" s="113"/>
+      <c r="Z7" s="122"/>
+      <c r="AA7" s="114"/>
       <c r="AB7" s="15">
         <v>2</v>
       </c>
@@ -14560,8 +14554,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU7" s="116"/>
-      <c r="AV7" s="113"/>
+      <c r="AU7" s="122"/>
+      <c r="AV7" s="114"/>
       <c r="AW7" s="15">
         <v>2</v>
       </c>
@@ -14637,8 +14631,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP7" s="116"/>
-      <c r="BQ7" s="113"/>
+      <c r="BP7" s="122"/>
+      <c r="BQ7" s="114"/>
       <c r="BR7" s="15">
         <v>2</v>
       </c>
@@ -14694,8 +14688,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG7" s="116"/>
-      <c r="CH7" s="113"/>
+      <c r="CG7" s="122"/>
+      <c r="CH7" s="114"/>
       <c r="CI7" s="15">
         <v>2</v>
       </c>
@@ -14771,8 +14765,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG7" s="116"/>
-      <c r="DH7" s="113"/>
+      <c r="DG7" s="122"/>
+      <c r="DH7" s="114"/>
       <c r="DI7" s="15">
         <v>2</v>
       </c>
@@ -14850,8 +14844,8 @@
       </c>
     </row>
     <row r="8" spans="5:131" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="116"/>
-      <c r="F8" s="113"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="114"/>
       <c r="G8" s="15">
         <v>3</v>
       </c>
@@ -14927,8 +14921,8 @@
         <f>TKB_LOP_SC!AQ8</f>
         <v>GVVN - Linh</v>
       </c>
-      <c r="Z8" s="116"/>
-      <c r="AA8" s="113"/>
+      <c r="Z8" s="122"/>
+      <c r="AA8" s="114"/>
       <c r="AB8" s="15">
         <v>3</v>
       </c>
@@ -15004,8 +14998,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU8" s="116"/>
-      <c r="AV8" s="113"/>
+      <c r="AU8" s="122"/>
+      <c r="AV8" s="114"/>
       <c r="AW8" s="15">
         <v>3</v>
       </c>
@@ -15081,8 +15075,8 @@
         <f t="shared" si="32"/>
         <v>Linh</v>
       </c>
-      <c r="BP8" s="116"/>
-      <c r="BQ8" s="113"/>
+      <c r="BP8" s="122"/>
+      <c r="BQ8" s="114"/>
       <c r="BR8" s="15">
         <v>3</v>
       </c>
@@ -15138,8 +15132,8 @@
         <f t="shared" si="44"/>
         <v>Hồng</v>
       </c>
-      <c r="CG8" s="116"/>
-      <c r="CH8" s="113"/>
+      <c r="CG8" s="122"/>
+      <c r="CH8" s="114"/>
       <c r="CI8" s="15">
         <v>3</v>
       </c>
@@ -15215,8 +15209,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG8" s="116"/>
-      <c r="DH8" s="113"/>
+      <c r="DG8" s="122"/>
+      <c r="DH8" s="114"/>
       <c r="DI8" s="15">
         <v>3</v>
       </c>
@@ -15294,8 +15288,8 @@
       </c>
     </row>
     <row r="9" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E9" s="116"/>
-      <c r="F9" s="113"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="114"/>
       <c r="G9" s="15">
         <v>4</v>
       </c>
@@ -15371,8 +15365,8 @@
         <f>TKB_LOP_SC!AQ9</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="113"/>
+      <c r="Z9" s="122"/>
+      <c r="AA9" s="114"/>
       <c r="AB9" s="15">
         <v>4</v>
       </c>
@@ -15448,8 +15442,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU9" s="116"/>
-      <c r="AV9" s="113"/>
+      <c r="AU9" s="122"/>
+      <c r="AV9" s="114"/>
       <c r="AW9" s="15">
         <v>4</v>
       </c>
@@ -15525,8 +15519,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP9" s="116"/>
-      <c r="BQ9" s="113"/>
+      <c r="BP9" s="122"/>
+      <c r="BQ9" s="114"/>
       <c r="BR9" s="15">
         <v>4</v>
       </c>
@@ -15582,8 +15576,8 @@
         <f t="shared" si="44"/>
         <v>Hồng</v>
       </c>
-      <c r="CG9" s="116"/>
-      <c r="CH9" s="113"/>
+      <c r="CG9" s="122"/>
+      <c r="CH9" s="114"/>
       <c r="CI9" s="15">
         <v>4</v>
       </c>
@@ -15659,8 +15653,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG9" s="116"/>
-      <c r="DH9" s="113"/>
+      <c r="DG9" s="122"/>
+      <c r="DH9" s="114"/>
       <c r="DI9" s="15">
         <v>4</v>
       </c>
@@ -15738,8 +15732,8 @@
       </c>
     </row>
     <row r="10" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="117"/>
-      <c r="F10" s="114"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="115"/>
       <c r="G10" s="16">
         <v>5</v>
       </c>
@@ -15815,8 +15809,8 @@
         <f>TKB_LOP_SC!AQ10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="114"/>
+      <c r="Z10" s="123"/>
+      <c r="AA10" s="115"/>
       <c r="AB10" s="16">
         <v>5</v>
       </c>
@@ -15892,8 +15886,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU10" s="117"/>
-      <c r="AV10" s="114"/>
+      <c r="AU10" s="123"/>
+      <c r="AV10" s="115"/>
       <c r="AW10" s="16">
         <v>5</v>
       </c>
@@ -15969,8 +15963,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP10" s="117"/>
-      <c r="BQ10" s="114"/>
+      <c r="BP10" s="123"/>
+      <c r="BQ10" s="115"/>
       <c r="BR10" s="16">
         <v>5</v>
       </c>
@@ -16026,8 +16020,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG10" s="117"/>
-      <c r="CH10" s="114"/>
+      <c r="CG10" s="123"/>
+      <c r="CH10" s="115"/>
       <c r="CI10" s="16">
         <v>5</v>
       </c>
@@ -16103,8 +16097,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG10" s="117"/>
-      <c r="DH10" s="114"/>
+      <c r="DG10" s="123"/>
+      <c r="DH10" s="115"/>
       <c r="DI10" s="16">
         <v>5</v>
       </c>
@@ -16183,7 +16177,7 @@
     </row>
     <row r="11" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E11" s="22"/>
-      <c r="F11" s="112" t="s">
+      <c r="F11" s="113" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="10">
@@ -16223,11 +16217,11 @@
       </c>
       <c r="P11" s="5" t="str">
         <f>TKB_LOP_SC!X6</f>
-        <v>GDĐP - Ánh NV</v>
+        <v>Tiếng Trung - Châu</v>
       </c>
       <c r="Q11" s="5" t="str">
         <f>TKB_LOP_SC!Z6</f>
-        <v>Tin - Nguyên</v>
+        <v>Văn - Ánh NV</v>
       </c>
       <c r="R11" s="31" t="str">
         <f>TKB_LOP_SC!AB6</f>
@@ -16262,7 +16256,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="22"/>
-      <c r="AA11" s="112" t="s">
+      <c r="AA11" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AB11" s="10">
@@ -16341,7 +16335,7 @@
         <v/>
       </c>
       <c r="AU11" s="55"/>
-      <c r="AV11" s="112" t="s">
+      <c r="AV11" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AW11" s="10">
@@ -16381,11 +16375,11 @@
       </c>
       <c r="BF11" s="29" t="str">
         <f t="shared" si="23"/>
-        <v>Ánh NV</v>
+        <v>Châu</v>
       </c>
       <c r="BG11" s="29" t="str">
         <f t="shared" si="24"/>
-        <v>Nguyên</v>
+        <v>Ánh NV</v>
       </c>
       <c r="BH11" s="29" t="str">
         <f t="shared" si="25"/>
@@ -16420,7 +16414,7 @@
         <v/>
       </c>
       <c r="BP11" s="55"/>
-      <c r="BQ11" s="112" t="s">
+      <c r="BQ11" s="113" t="s">
         <v>4</v>
       </c>
       <c r="BR11" s="10">
@@ -16460,11 +16454,11 @@
       </c>
       <c r="CA11" s="29" t="str">
         <f t="shared" si="40"/>
-        <v>Ánh NV</v>
+        <v>Châu</v>
       </c>
       <c r="CB11" s="29" t="str">
         <f t="shared" si="41"/>
-        <v>Nguyên</v>
+        <v>Ánh NV</v>
       </c>
       <c r="CC11" s="29" t="str">
         <f t="shared" si="42"/>
@@ -16479,7 +16473,7 @@
         <v>MN1</v>
       </c>
       <c r="CG11" s="55"/>
-      <c r="CH11" s="112" t="s">
+      <c r="CH11" s="113" t="s">
         <v>4</v>
       </c>
       <c r="CI11" s="10">
@@ -16558,7 +16552,7 @@
         <v>0</v>
       </c>
       <c r="DG11" s="66"/>
-      <c r="DH11" s="112" t="s">
+      <c r="DH11" s="113" t="s">
         <v>4</v>
       </c>
       <c r="DI11" s="10">
@@ -16639,7 +16633,7 @@
     </row>
     <row r="12" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="22"/>
-      <c r="F12" s="113"/>
+      <c r="F12" s="114"/>
       <c r="G12" s="15">
         <v>2</v>
       </c>
@@ -16681,7 +16675,7 @@
       </c>
       <c r="Q12" s="5" t="str">
         <f>TKB_LOP_SC!Z7</f>
-        <v>Văn - Ánh NV</v>
+        <v>HĐTN - Phương Anh</v>
       </c>
       <c r="R12" s="31" t="str">
         <f>TKB_LOP_SC!AB7</f>
@@ -16716,7 +16710,7 @@
         <v>GVNN - Aziz, Phượng</v>
       </c>
       <c r="Z12" s="22"/>
-      <c r="AA12" s="113"/>
+      <c r="AA12" s="114"/>
       <c r="AB12" s="15">
         <v>2</v>
       </c>
@@ -16793,7 +16787,7 @@
         <v/>
       </c>
       <c r="AU12" s="55"/>
-      <c r="AV12" s="113"/>
+      <c r="AV12" s="114"/>
       <c r="AW12" s="15">
         <v>2</v>
       </c>
@@ -16835,7 +16829,7 @@
       </c>
       <c r="BG12" s="29" t="str">
         <f t="shared" si="24"/>
-        <v>Ánh NV</v>
+        <v>Phương Anh</v>
       </c>
       <c r="BH12" s="29" t="str">
         <f t="shared" si="25"/>
@@ -16870,7 +16864,7 @@
         <v>Aziz, Phượng</v>
       </c>
       <c r="BP12" s="55"/>
-      <c r="BQ12" s="113"/>
+      <c r="BQ12" s="114"/>
       <c r="BR12" s="15">
         <v>2</v>
       </c>
@@ -16912,7 +16906,7 @@
       </c>
       <c r="CB12" s="29" t="str">
         <f t="shared" si="41"/>
-        <v>Ánh NV</v>
+        <v>Phương Anh</v>
       </c>
       <c r="CC12" s="29" t="str">
         <f t="shared" si="42"/>
@@ -16927,7 +16921,7 @@
         <v>Trang</v>
       </c>
       <c r="CG12" s="55"/>
-      <c r="CH12" s="113"/>
+      <c r="CH12" s="114"/>
       <c r="CI12" s="15">
         <v>2</v>
       </c>
@@ -17004,7 +16998,7 @@
         <v>0</v>
       </c>
       <c r="DG12" s="66"/>
-      <c r="DH12" s="113"/>
+      <c r="DH12" s="114"/>
       <c r="DI12" s="15">
         <v>2</v>
       </c>
@@ -17083,7 +17077,7 @@
     </row>
     <row r="13" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="22"/>
-      <c r="F13" s="113"/>
+      <c r="F13" s="114"/>
       <c r="G13" s="15">
         <v>3</v>
       </c>
@@ -17160,7 +17154,7 @@
         <v>0</v>
       </c>
       <c r="Z13" s="22"/>
-      <c r="AA13" s="113"/>
+      <c r="AA13" s="114"/>
       <c r="AB13" s="15">
         <v>3</v>
       </c>
@@ -17237,7 +17231,7 @@
         <v/>
       </c>
       <c r="AU13" s="55"/>
-      <c r="AV13" s="113"/>
+      <c r="AV13" s="114"/>
       <c r="AW13" s="15">
         <v>3</v>
       </c>
@@ -17314,7 +17308,7 @@
         <v/>
       </c>
       <c r="BP13" s="55"/>
-      <c r="BQ13" s="113"/>
+      <c r="BQ13" s="114"/>
       <c r="BR13" s="15">
         <v>3</v>
       </c>
@@ -17371,7 +17365,7 @@
         <v>MN1</v>
       </c>
       <c r="CG13" s="55"/>
-      <c r="CH13" s="113"/>
+      <c r="CH13" s="114"/>
       <c r="CI13" s="15">
         <v>3</v>
       </c>
@@ -17448,7 +17442,7 @@
         <v>0</v>
       </c>
       <c r="DG13" s="66"/>
-      <c r="DH13" s="113"/>
+      <c r="DH13" s="114"/>
       <c r="DI13" s="15">
         <v>3</v>
       </c>
@@ -17527,7 +17521,7 @@
     </row>
     <row r="14" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" s="22"/>
-      <c r="F14" s="113"/>
+      <c r="F14" s="114"/>
       <c r="G14" s="15">
         <v>4</v>
       </c>
@@ -17565,7 +17559,7 @@
       </c>
       <c r="P14" s="5" t="str">
         <f>TKB_LOP_SC!X9</f>
-        <v>Tiếng Trung - Châu</v>
+        <v>GDĐP - Ánh NV</v>
       </c>
       <c r="Q14" s="5" t="str">
         <f>TKB_LOP_SC!Z9</f>
@@ -17604,7 +17598,7 @@
         <v>0</v>
       </c>
       <c r="Z14" s="22"/>
-      <c r="AA14" s="113"/>
+      <c r="AA14" s="114"/>
       <c r="AB14" s="15">
         <v>4</v>
       </c>
@@ -17681,7 +17675,7 @@
         <v/>
       </c>
       <c r="AU14" s="55"/>
-      <c r="AV14" s="113"/>
+      <c r="AV14" s="114"/>
       <c r="AW14" s="15">
         <v>4</v>
       </c>
@@ -17719,7 +17713,7 @@
       </c>
       <c r="BF14" s="29" t="str">
         <f t="shared" si="23"/>
-        <v>Châu</v>
+        <v>Ánh NV</v>
       </c>
       <c r="BG14" s="29" t="str">
         <f t="shared" si="24"/>
@@ -17758,7 +17752,7 @@
         <v/>
       </c>
       <c r="BP14" s="55"/>
-      <c r="BQ14" s="113"/>
+      <c r="BQ14" s="114"/>
       <c r="BR14" s="15">
         <v>4</v>
       </c>
@@ -17796,7 +17790,7 @@
       </c>
       <c r="CA14" s="29" t="str">
         <f t="shared" si="40"/>
-        <v>Châu</v>
+        <v>Ánh NV</v>
       </c>
       <c r="CB14" s="29" t="str">
         <f t="shared" si="41"/>
@@ -17815,7 +17809,7 @@
         <v>Huyền</v>
       </c>
       <c r="CG14" s="55"/>
-      <c r="CH14" s="113"/>
+      <c r="CH14" s="114"/>
       <c r="CI14" s="15">
         <v>4</v>
       </c>
@@ -17892,7 +17886,7 @@
         <v>0</v>
       </c>
       <c r="DG14" s="66"/>
-      <c r="DH14" s="113"/>
+      <c r="DH14" s="114"/>
       <c r="DI14" s="15">
         <v>4</v>
       </c>
@@ -17971,7 +17965,7 @@
     </row>
     <row r="15" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E15" s="22"/>
-      <c r="F15" s="114"/>
+      <c r="F15" s="115"/>
       <c r="G15" s="16">
         <v>5</v>
       </c>
@@ -18048,7 +18042,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="22"/>
-      <c r="AA15" s="114"/>
+      <c r="AA15" s="115"/>
       <c r="AB15" s="16">
         <v>5</v>
       </c>
@@ -18125,7 +18119,7 @@
         <v/>
       </c>
       <c r="AU15" s="55"/>
-      <c r="AV15" s="114"/>
+      <c r="AV15" s="115"/>
       <c r="AW15" s="16">
         <v>5</v>
       </c>
@@ -18202,7 +18196,7 @@
         <v/>
       </c>
       <c r="BP15" s="55"/>
-      <c r="BQ15" s="114"/>
+      <c r="BQ15" s="115"/>
       <c r="BR15" s="16">
         <v>5</v>
       </c>
@@ -18259,7 +18253,7 @@
         <v/>
       </c>
       <c r="CG15" s="55"/>
-      <c r="CH15" s="114"/>
+      <c r="CH15" s="115"/>
       <c r="CI15" s="16">
         <v>5</v>
       </c>
@@ -18336,7 +18330,7 @@
         <v/>
       </c>
       <c r="DG15" s="66"/>
-      <c r="DH15" s="114"/>
+      <c r="DH15" s="115"/>
       <c r="DI15" s="16">
         <v>5</v>
       </c>
@@ -18414,10 +18408,10 @@
       </c>
     </row>
     <row r="16" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E16" s="109">
-        <v>3</v>
-      </c>
-      <c r="F16" s="112" t="s">
+      <c r="E16" s="116">
+        <v>3</v>
+      </c>
+      <c r="F16" s="113" t="s">
         <v>3</v>
       </c>
       <c r="G16" s="10">
@@ -18479,9 +18473,9 @@
         <f>TKB_LOP_SC!AI11</f>
         <v>Tìm hiểu thiên nhiên - MN2</v>
       </c>
-      <c r="V16" s="2">
+      <c r="V16" s="2" t="str">
         <f>TKB_LOP_SC!AK11</f>
-        <v>0</v>
+        <v>GVVN - Linh</v>
       </c>
       <c r="W16" s="2">
         <f>TKB_LOP_SC!AM11</f>
@@ -18495,10 +18489,10 @@
         <f>TKB_LOP_SC!AQ11</f>
         <v>GVNN - Aziz, Phượng</v>
       </c>
-      <c r="Z16" s="109">
-        <v>3</v>
-      </c>
-      <c r="AA16" s="112" t="s">
+      <c r="Z16" s="116">
+        <v>3</v>
+      </c>
+      <c r="AA16" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AB16" s="10">
@@ -18576,10 +18570,10 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU16" s="109">
-        <v>3</v>
-      </c>
-      <c r="AV16" s="112" t="s">
+      <c r="AU16" s="116">
+        <v>3</v>
+      </c>
+      <c r="AV16" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AW16" s="10">
@@ -18643,7 +18637,7 @@
       </c>
       <c r="BL16" s="29" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Linh</v>
       </c>
       <c r="BM16" s="29" t="str">
         <f t="shared" si="30"/>
@@ -18657,10 +18651,10 @@
         <f t="shared" si="32"/>
         <v>Aziz, Phượng</v>
       </c>
-      <c r="BP16" s="109">
-        <v>3</v>
-      </c>
-      <c r="BQ16" s="112" t="s">
+      <c r="BP16" s="116">
+        <v>3</v>
+      </c>
+      <c r="BQ16" s="113" t="s">
         <v>3</v>
       </c>
       <c r="BR16" s="10">
@@ -18718,10 +18712,10 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG16" s="109">
-        <v>3</v>
-      </c>
-      <c r="CH16" s="112" t="s">
+      <c r="CG16" s="116">
+        <v>3</v>
+      </c>
+      <c r="CH16" s="113" t="s">
         <v>3</v>
       </c>
       <c r="CI16" s="10">
@@ -18799,10 +18793,10 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG16" s="109">
-        <v>3</v>
-      </c>
-      <c r="DH16" s="112" t="s">
+      <c r="DG16" s="116">
+        <v>3</v>
+      </c>
+      <c r="DH16" s="113" t="s">
         <v>3</v>
       </c>
       <c r="DI16" s="10">
@@ -18882,8 +18876,8 @@
       </c>
     </row>
     <row r="17" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E17" s="110"/>
-      <c r="F17" s="113"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="114"/>
       <c r="G17" s="15">
         <v>2</v>
       </c>
@@ -18959,8 +18953,8 @@
         <f>TKB_LOP_SC!AQ12</f>
         <v>0</v>
       </c>
-      <c r="Z17" s="110"/>
-      <c r="AA17" s="113"/>
+      <c r="Z17" s="117"/>
+      <c r="AA17" s="114"/>
       <c r="AB17" s="15">
         <v>2</v>
       </c>
@@ -19036,8 +19030,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU17" s="110"/>
-      <c r="AV17" s="113"/>
+      <c r="AU17" s="117"/>
+      <c r="AV17" s="114"/>
       <c r="AW17" s="15">
         <v>2</v>
       </c>
@@ -19113,8 +19107,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP17" s="110"/>
-      <c r="BQ17" s="113"/>
+      <c r="BP17" s="117"/>
+      <c r="BQ17" s="114"/>
       <c r="BR17" s="15">
         <v>2</v>
       </c>
@@ -19170,8 +19164,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG17" s="110"/>
-      <c r="CH17" s="113"/>
+      <c r="CG17" s="117"/>
+      <c r="CH17" s="114"/>
       <c r="CI17" s="15">
         <v>2</v>
       </c>
@@ -19247,8 +19241,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG17" s="110"/>
-      <c r="DH17" s="113"/>
+      <c r="DG17" s="117"/>
+      <c r="DH17" s="114"/>
       <c r="DI17" s="15">
         <v>2</v>
       </c>
@@ -19326,8 +19320,8 @@
       </c>
     </row>
     <row r="18" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E18" s="110"/>
-      <c r="F18" s="113"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="114"/>
       <c r="G18" s="15">
         <v>3</v>
       </c>
@@ -19399,12 +19393,12 @@
         <f>TKB_LOP_SC!AO13</f>
         <v>GVVN - Linh</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y18" s="2" t="str">
         <f>TKB_LOP_SC!AR13</f>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="113"/>
+        <v>GVVN - Linh</v>
+      </c>
+      <c r="Z18" s="117"/>
+      <c r="AA18" s="114"/>
       <c r="AB18" s="15">
         <v>3</v>
       </c>
@@ -19480,8 +19474,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU18" s="110"/>
-      <c r="AV18" s="113"/>
+      <c r="AU18" s="117"/>
+      <c r="AV18" s="114"/>
       <c r="AW18" s="15">
         <v>3</v>
       </c>
@@ -19555,10 +19549,10 @@
       </c>
       <c r="BO18" s="29" t="str">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BP18" s="110"/>
-      <c r="BQ18" s="113"/>
+        <v>Linh</v>
+      </c>
+      <c r="BP18" s="117"/>
+      <c r="BQ18" s="114"/>
       <c r="BR18" s="15">
         <v>3</v>
       </c>
@@ -19614,8 +19608,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG18" s="110"/>
-      <c r="CH18" s="113"/>
+      <c r="CG18" s="117"/>
+      <c r="CH18" s="114"/>
       <c r="CI18" s="15">
         <v>3</v>
       </c>
@@ -19691,8 +19685,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG18" s="110"/>
-      <c r="DH18" s="113"/>
+      <c r="DG18" s="117"/>
+      <c r="DH18" s="114"/>
       <c r="DI18" s="15">
         <v>3</v>
       </c>
@@ -19770,8 +19764,8 @@
       </c>
     </row>
     <row r="19" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="110"/>
-      <c r="F19" s="113"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="114"/>
       <c r="G19" s="15">
         <v>4</v>
       </c>
@@ -19847,8 +19841,8 @@
         <f>TKB_LOP_SC!AQ14</f>
         <v>0</v>
       </c>
-      <c r="Z19" s="110"/>
-      <c r="AA19" s="113"/>
+      <c r="Z19" s="117"/>
+      <c r="AA19" s="114"/>
       <c r="AB19" s="15">
         <v>4</v>
       </c>
@@ -19924,8 +19918,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="113"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="114"/>
       <c r="AW19" s="15">
         <v>4</v>
       </c>
@@ -20001,8 +19995,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP19" s="110"/>
-      <c r="BQ19" s="113"/>
+      <c r="BP19" s="117"/>
+      <c r="BQ19" s="114"/>
       <c r="BR19" s="15">
         <v>4</v>
       </c>
@@ -20058,8 +20052,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG19" s="110"/>
-      <c r="CH19" s="113"/>
+      <c r="CG19" s="117"/>
+      <c r="CH19" s="114"/>
       <c r="CI19" s="15">
         <v>4</v>
       </c>
@@ -20135,8 +20129,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG19" s="110"/>
-      <c r="DH19" s="113"/>
+      <c r="DG19" s="117"/>
+      <c r="DH19" s="114"/>
       <c r="DI19" s="15">
         <v>4</v>
       </c>
@@ -20214,8 +20208,8 @@
       </c>
     </row>
     <row r="20" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="111"/>
-      <c r="F20" s="114"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="16">
         <v>5</v>
       </c>
@@ -20291,8 +20285,8 @@
         <f>TKB_LOP_SC!AQ15</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="111"/>
-      <c r="AA20" s="114"/>
+      <c r="Z20" s="118"/>
+      <c r="AA20" s="115"/>
       <c r="AB20" s="16">
         <v>5</v>
       </c>
@@ -20368,8 +20362,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU20" s="111"/>
-      <c r="AV20" s="114"/>
+      <c r="AU20" s="118"/>
+      <c r="AV20" s="115"/>
       <c r="AW20" s="16">
         <v>5</v>
       </c>
@@ -20445,8 +20439,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP20" s="111"/>
-      <c r="BQ20" s="114"/>
+      <c r="BP20" s="118"/>
+      <c r="BQ20" s="115"/>
       <c r="BR20" s="16">
         <v>5</v>
       </c>
@@ -20502,8 +20496,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG20" s="111"/>
-      <c r="CH20" s="114"/>
+      <c r="CG20" s="118"/>
+      <c r="CH20" s="115"/>
       <c r="CI20" s="16">
         <v>5</v>
       </c>
@@ -20579,8 +20573,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG20" s="111"/>
-      <c r="DH20" s="114"/>
+      <c r="DG20" s="118"/>
+      <c r="DH20" s="115"/>
       <c r="DI20" s="16">
         <v>5</v>
       </c>
@@ -20659,7 +20653,7 @@
     </row>
     <row r="21" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E21" s="22"/>
-      <c r="F21" s="112" t="s">
+      <c r="F21" s="113" t="s">
         <v>4</v>
       </c>
       <c r="G21" s="10">
@@ -20738,7 +20732,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="22"/>
-      <c r="AA21" s="112" t="s">
+      <c r="AA21" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AB21" s="10">
@@ -20817,7 +20811,7 @@
         <v/>
       </c>
       <c r="AU21" s="55"/>
-      <c r="AV21" s="112" t="s">
+      <c r="AV21" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AW21" s="10">
@@ -20896,7 +20890,7 @@
         <v/>
       </c>
       <c r="BP21" s="55"/>
-      <c r="BQ21" s="112" t="s">
+      <c r="BQ21" s="113" t="s">
         <v>4</v>
       </c>
       <c r="BR21" s="10">
@@ -20955,7 +20949,7 @@
         <v>MN1</v>
       </c>
       <c r="CG21" s="55"/>
-      <c r="CH21" s="112" t="s">
+      <c r="CH21" s="113" t="s">
         <v>4</v>
       </c>
       <c r="CI21" s="10">
@@ -21034,7 +21028,7 @@
         <v>0</v>
       </c>
       <c r="DG21" s="66"/>
-      <c r="DH21" s="112" t="s">
+      <c r="DH21" s="113" t="s">
         <v>4</v>
       </c>
       <c r="DI21" s="10">
@@ -21115,7 +21109,7 @@
     </row>
     <row r="22" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E22" s="22"/>
-      <c r="F22" s="113"/>
+      <c r="F22" s="114"/>
       <c r="G22" s="15">
         <v>2</v>
       </c>
@@ -21192,7 +21186,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="22"/>
-      <c r="AA22" s="113"/>
+      <c r="AA22" s="114"/>
       <c r="AB22" s="15">
         <v>2</v>
       </c>
@@ -21269,7 +21263,7 @@
         <v/>
       </c>
       <c r="AU22" s="55"/>
-      <c r="AV22" s="113"/>
+      <c r="AV22" s="114"/>
       <c r="AW22" s="15">
         <v>2</v>
       </c>
@@ -21346,7 +21340,7 @@
         <v/>
       </c>
       <c r="BP22" s="55"/>
-      <c r="BQ22" s="113"/>
+      <c r="BQ22" s="114"/>
       <c r="BR22" s="15">
         <v>2</v>
       </c>
@@ -21403,7 +21397,7 @@
         <v>MN1</v>
       </c>
       <c r="CG22" s="55"/>
-      <c r="CH22" s="113"/>
+      <c r="CH22" s="114"/>
       <c r="CI22" s="15">
         <v>2</v>
       </c>
@@ -21480,7 +21474,7 @@
         <v>0</v>
       </c>
       <c r="DG22" s="66"/>
-      <c r="DH22" s="113"/>
+      <c r="DH22" s="114"/>
       <c r="DI22" s="15">
         <v>2</v>
       </c>
@@ -21559,7 +21553,7 @@
     </row>
     <row r="23" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E23" s="22"/>
-      <c r="F23" s="113"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="15">
         <v>3</v>
       </c>
@@ -21636,7 +21630,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z23" s="22"/>
-      <c r="AA23" s="113"/>
+      <c r="AA23" s="114"/>
       <c r="AB23" s="15">
         <v>3</v>
       </c>
@@ -21713,7 +21707,7 @@
         <v/>
       </c>
       <c r="AU23" s="55"/>
-      <c r="AV23" s="113"/>
+      <c r="AV23" s="114"/>
       <c r="AW23" s="15">
         <v>3</v>
       </c>
@@ -21790,7 +21784,7 @@
         <v/>
       </c>
       <c r="BP23" s="55"/>
-      <c r="BQ23" s="113"/>
+      <c r="BQ23" s="114"/>
       <c r="BR23" s="15">
         <v>3</v>
       </c>
@@ -21847,7 +21841,7 @@
         <v>Trang</v>
       </c>
       <c r="CG23" s="55"/>
-      <c r="CH23" s="113"/>
+      <c r="CH23" s="114"/>
       <c r="CI23" s="15">
         <v>3</v>
       </c>
@@ -21924,7 +21918,7 @@
         <v>0</v>
       </c>
       <c r="DG23" s="66"/>
-      <c r="DH23" s="113"/>
+      <c r="DH23" s="114"/>
       <c r="DI23" s="15">
         <v>3</v>
       </c>
@@ -22003,7 +21997,7 @@
     </row>
     <row r="24" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E24" s="22"/>
-      <c r="F24" s="113"/>
+      <c r="F24" s="114"/>
       <c r="G24" s="15">
         <v>4</v>
       </c>
@@ -22075,12 +22069,12 @@
         <f>TKB_LOP_SC!AP14</f>
         <v>0</v>
       </c>
-      <c r="Y24" s="2" t="str">
+      <c r="Y24" s="2">
         <f>TKB_LOP_SC!AQ19</f>
-        <v>GVVN - Linh</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="22"/>
-      <c r="AA24" s="113"/>
+      <c r="AA24" s="114"/>
       <c r="AB24" s="15">
         <v>4</v>
       </c>
@@ -22157,7 +22151,7 @@
         <v/>
       </c>
       <c r="AU24" s="55"/>
-      <c r="AV24" s="113"/>
+      <c r="AV24" s="114"/>
       <c r="AW24" s="15">
         <v>4</v>
       </c>
@@ -22231,10 +22225,10 @@
       </c>
       <c r="BO24" s="29" t="str">
         <f t="shared" si="32"/>
-        <v>Linh</v>
+        <v/>
       </c>
       <c r="BP24" s="55"/>
-      <c r="BQ24" s="113"/>
+      <c r="BQ24" s="114"/>
       <c r="BR24" s="15">
         <v>4</v>
       </c>
@@ -22291,7 +22285,7 @@
         <v>MN1</v>
       </c>
       <c r="CG24" s="55"/>
-      <c r="CH24" s="113"/>
+      <c r="CH24" s="114"/>
       <c r="CI24" s="15">
         <v>4</v>
       </c>
@@ -22368,7 +22362,7 @@
         <v>0</v>
       </c>
       <c r="DG24" s="66"/>
-      <c r="DH24" s="113"/>
+      <c r="DH24" s="114"/>
       <c r="DI24" s="15">
         <v>4</v>
       </c>
@@ -22447,7 +22441,7 @@
     </row>
     <row r="25" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E25" s="22"/>
-      <c r="F25" s="114"/>
+      <c r="F25" s="115"/>
       <c r="G25" s="16">
         <v>5</v>
       </c>
@@ -22524,7 +22518,7 @@
         <v>0</v>
       </c>
       <c r="Z25" s="22"/>
-      <c r="AA25" s="114"/>
+      <c r="AA25" s="115"/>
       <c r="AB25" s="16">
         <v>5</v>
       </c>
@@ -22601,7 +22595,7 @@
         <v/>
       </c>
       <c r="AU25" s="55"/>
-      <c r="AV25" s="114"/>
+      <c r="AV25" s="115"/>
       <c r="AW25" s="16">
         <v>5</v>
       </c>
@@ -22678,7 +22672,7 @@
         <v/>
       </c>
       <c r="BP25" s="55"/>
-      <c r="BQ25" s="114"/>
+      <c r="BQ25" s="115"/>
       <c r="BR25" s="16">
         <v>5</v>
       </c>
@@ -22735,7 +22729,7 @@
         <v/>
       </c>
       <c r="CG25" s="55"/>
-      <c r="CH25" s="114"/>
+      <c r="CH25" s="115"/>
       <c r="CI25" s="16">
         <v>5</v>
       </c>
@@ -22812,7 +22806,7 @@
         <v/>
       </c>
       <c r="DG25" s="66"/>
-      <c r="DH25" s="114"/>
+      <c r="DH25" s="115"/>
       <c r="DI25" s="16">
         <v>5</v>
       </c>
@@ -22890,10 +22884,10 @@
       </c>
     </row>
     <row r="26" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E26" s="109">
-        <v>4</v>
-      </c>
-      <c r="F26" s="112" t="s">
+      <c r="E26" s="116">
+        <v>4</v>
+      </c>
+      <c r="F26" s="113" t="s">
         <v>3</v>
       </c>
       <c r="G26" s="10">
@@ -22971,10 +22965,10 @@
         <f>TKB_LOP_SC!AQ16</f>
         <v>0</v>
       </c>
-      <c r="Z26" s="109">
-        <v>4</v>
-      </c>
-      <c r="AA26" s="112" t="s">
+      <c r="Z26" s="116">
+        <v>4</v>
+      </c>
+      <c r="AA26" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="10">
@@ -23052,10 +23046,10 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU26" s="109">
-        <v>4</v>
-      </c>
-      <c r="AV26" s="112" t="s">
+      <c r="AU26" s="116">
+        <v>4</v>
+      </c>
+      <c r="AV26" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AW26" s="10">
@@ -23133,10 +23127,10 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP26" s="109">
-        <v>4</v>
-      </c>
-      <c r="BQ26" s="112" t="s">
+      <c r="BP26" s="116">
+        <v>4</v>
+      </c>
+      <c r="BQ26" s="113" t="s">
         <v>3</v>
       </c>
       <c r="BR26" s="10">
@@ -23194,10 +23188,10 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG26" s="109">
-        <v>4</v>
-      </c>
-      <c r="CH26" s="112" t="s">
+      <c r="CG26" s="116">
+        <v>4</v>
+      </c>
+      <c r="CH26" s="113" t="s">
         <v>3</v>
       </c>
       <c r="CI26" s="10">
@@ -23275,10 +23269,10 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG26" s="109">
-        <v>4</v>
-      </c>
-      <c r="DH26" s="112" t="s">
+      <c r="DG26" s="116">
+        <v>4</v>
+      </c>
+      <c r="DH26" s="113" t="s">
         <v>3</v>
       </c>
       <c r="DI26" s="10">
@@ -23358,8 +23352,8 @@
       </c>
     </row>
     <row r="27" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E27" s="110"/>
-      <c r="F27" s="113"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="114"/>
       <c r="G27" s="15">
         <v>2</v>
       </c>
@@ -23393,7 +23387,7 @@
       </c>
       <c r="O27" s="11" t="str">
         <f>TKB_LOP_SC!S17</f>
-        <v>TViệt - Ly</v>
+        <v>TViệt - Ngọc</v>
       </c>
       <c r="P27" s="5" t="str">
         <f>TKB_LOP_SC!W17</f>
@@ -23435,8 +23429,8 @@
         <f>TKB_LOP_SC!AQ17</f>
         <v>0</v>
       </c>
-      <c r="Z27" s="110"/>
-      <c r="AA27" s="113"/>
+      <c r="Z27" s="117"/>
+      <c r="AA27" s="114"/>
       <c r="AB27" s="15">
         <v>2</v>
       </c>
@@ -23512,8 +23506,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU27" s="110"/>
-      <c r="AV27" s="113"/>
+      <c r="AU27" s="117"/>
+      <c r="AV27" s="114"/>
       <c r="AW27" s="15">
         <v>2</v>
       </c>
@@ -23547,7 +23541,7 @@
       </c>
       <c r="BE27" s="29" t="str">
         <f t="shared" si="22"/>
-        <v>Ly</v>
+        <v>Ngọc</v>
       </c>
       <c r="BF27" s="29" t="str">
         <f t="shared" si="23"/>
@@ -23589,8 +23583,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP27" s="110"/>
-      <c r="BQ27" s="113"/>
+      <c r="BP27" s="117"/>
+      <c r="BQ27" s="114"/>
       <c r="BR27" s="15">
         <v>2</v>
       </c>
@@ -23624,7 +23618,7 @@
       </c>
       <c r="BZ27" s="29" t="str">
         <f t="shared" si="39"/>
-        <v>Ly</v>
+        <v>Ngọc</v>
       </c>
       <c r="CA27" s="29" t="str">
         <f t="shared" si="40"/>
@@ -23646,8 +23640,8 @@
         <f t="shared" si="44"/>
         <v>Huyền</v>
       </c>
-      <c r="CG27" s="110"/>
-      <c r="CH27" s="113"/>
+      <c r="CG27" s="117"/>
+      <c r="CH27" s="114"/>
       <c r="CI27" s="15">
         <v>2</v>
       </c>
@@ -23723,8 +23717,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG27" s="110"/>
-      <c r="DH27" s="113"/>
+      <c r="DG27" s="117"/>
+      <c r="DH27" s="114"/>
       <c r="DI27" s="15">
         <v>2</v>
       </c>
@@ -23802,8 +23796,8 @@
       </c>
     </row>
     <row r="28" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="110"/>
-      <c r="F28" s="113"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="114"/>
       <c r="G28" s="15">
         <v>3</v>
       </c>
@@ -23879,8 +23873,8 @@
         <f>TKB_LOP_SC!AQ18</f>
         <v>0</v>
       </c>
-      <c r="Z28" s="110"/>
-      <c r="AA28" s="113"/>
+      <c r="Z28" s="117"/>
+      <c r="AA28" s="114"/>
       <c r="AB28" s="15">
         <v>3</v>
       </c>
@@ -23956,8 +23950,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU28" s="110"/>
-      <c r="AV28" s="113"/>
+      <c r="AU28" s="117"/>
+      <c r="AV28" s="114"/>
       <c r="AW28" s="15">
         <v>3</v>
       </c>
@@ -24033,8 +24027,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP28" s="110"/>
-      <c r="BQ28" s="113"/>
+      <c r="BP28" s="117"/>
+      <c r="BQ28" s="114"/>
       <c r="BR28" s="15">
         <v>3</v>
       </c>
@@ -24090,8 +24084,8 @@
         <f t="shared" si="44"/>
         <v>Trang</v>
       </c>
-      <c r="CG28" s="110"/>
-      <c r="CH28" s="113"/>
+      <c r="CG28" s="117"/>
+      <c r="CH28" s="114"/>
       <c r="CI28" s="15">
         <v>3</v>
       </c>
@@ -24167,8 +24161,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG28" s="110"/>
-      <c r="DH28" s="113"/>
+      <c r="DG28" s="117"/>
+      <c r="DH28" s="114"/>
       <c r="DI28" s="15">
         <v>3</v>
       </c>
@@ -24246,8 +24240,8 @@
       </c>
     </row>
     <row r="29" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="110"/>
-      <c r="F29" s="113"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="114"/>
       <c r="G29" s="15">
         <v>4</v>
       </c>
@@ -24323,8 +24317,8 @@
         <f>TKB_LOP_SC!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="Z29" s="110"/>
-      <c r="AA29" s="113"/>
+      <c r="Z29" s="117"/>
+      <c r="AA29" s="114"/>
       <c r="AB29" s="15">
         <v>4</v>
       </c>
@@ -24400,8 +24394,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU29" s="110"/>
-      <c r="AV29" s="113"/>
+      <c r="AU29" s="117"/>
+      <c r="AV29" s="114"/>
       <c r="AW29" s="15">
         <v>4</v>
       </c>
@@ -24477,8 +24471,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP29" s="110"/>
-      <c r="BQ29" s="113"/>
+      <c r="BP29" s="117"/>
+      <c r="BQ29" s="114"/>
       <c r="BR29" s="15">
         <v>4</v>
       </c>
@@ -24534,8 +24528,8 @@
         <f t="shared" si="44"/>
         <v>Phương</v>
       </c>
-      <c r="CG29" s="110"/>
-      <c r="CH29" s="113"/>
+      <c r="CG29" s="117"/>
+      <c r="CH29" s="114"/>
       <c r="CI29" s="15">
         <v>4</v>
       </c>
@@ -24611,8 +24605,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG29" s="110"/>
-      <c r="DH29" s="113"/>
+      <c r="DG29" s="117"/>
+      <c r="DH29" s="114"/>
       <c r="DI29" s="15">
         <v>4</v>
       </c>
@@ -24690,8 +24684,8 @@
       </c>
     </row>
     <row r="30" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E30" s="111"/>
-      <c r="F30" s="114"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="115"/>
       <c r="G30" s="16">
         <v>5</v>
       </c>
@@ -24767,8 +24761,8 @@
         <f>TKB_LOP_SC!AQ20</f>
         <v>0</v>
       </c>
-      <c r="Z30" s="111"/>
-      <c r="AA30" s="114"/>
+      <c r="Z30" s="118"/>
+      <c r="AA30" s="115"/>
       <c r="AB30" s="16">
         <v>5</v>
       </c>
@@ -24844,8 +24838,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU30" s="111"/>
-      <c r="AV30" s="114"/>
+      <c r="AU30" s="118"/>
+      <c r="AV30" s="115"/>
       <c r="AW30" s="16">
         <v>5</v>
       </c>
@@ -24921,8 +24915,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP30" s="111"/>
-      <c r="BQ30" s="114"/>
+      <c r="BP30" s="118"/>
+      <c r="BQ30" s="115"/>
       <c r="BR30" s="16">
         <v>5</v>
       </c>
@@ -24978,8 +24972,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG30" s="111"/>
-      <c r="CH30" s="114"/>
+      <c r="CG30" s="118"/>
+      <c r="CH30" s="115"/>
       <c r="CI30" s="16">
         <v>5</v>
       </c>
@@ -25055,8 +25049,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG30" s="111"/>
-      <c r="DH30" s="114"/>
+      <c r="DG30" s="118"/>
+      <c r="DH30" s="115"/>
       <c r="DI30" s="16">
         <v>5</v>
       </c>
@@ -25135,7 +25129,7 @@
     </row>
     <row r="31" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E31" s="22"/>
-      <c r="F31" s="112" t="s">
+      <c r="F31" s="113" t="s">
         <v>4</v>
       </c>
       <c r="G31" s="10">
@@ -25214,7 +25208,7 @@
         <v>0</v>
       </c>
       <c r="Z31" s="22"/>
-      <c r="AA31" s="112" t="s">
+      <c r="AA31" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AB31" s="10">
@@ -25293,7 +25287,7 @@
         <v/>
       </c>
       <c r="AU31" s="55"/>
-      <c r="AV31" s="112" t="s">
+      <c r="AV31" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AW31" s="10">
@@ -25372,7 +25366,7 @@
         <v/>
       </c>
       <c r="BP31" s="55"/>
-      <c r="BQ31" s="112" t="s">
+      <c r="BQ31" s="113" t="s">
         <v>4</v>
       </c>
       <c r="BR31" s="10">
@@ -25431,7 +25425,7 @@
         <v>MN1</v>
       </c>
       <c r="CG31" s="55"/>
-      <c r="CH31" s="112" t="s">
+      <c r="CH31" s="113" t="s">
         <v>4</v>
       </c>
       <c r="CI31" s="10">
@@ -25510,7 +25504,7 @@
         <v>0</v>
       </c>
       <c r="DG31" s="66"/>
-      <c r="DH31" s="112" t="s">
+      <c r="DH31" s="113" t="s">
         <v>4</v>
       </c>
       <c r="DI31" s="10">
@@ -25591,7 +25585,7 @@
     </row>
     <row r="32" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E32" s="22"/>
-      <c r="F32" s="113"/>
+      <c r="F32" s="114"/>
       <c r="G32" s="15">
         <v>2</v>
       </c>
@@ -25668,7 +25662,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="22"/>
-      <c r="AA32" s="113"/>
+      <c r="AA32" s="114"/>
       <c r="AB32" s="15">
         <v>2</v>
       </c>
@@ -25745,7 +25739,7 @@
         <v/>
       </c>
       <c r="AU32" s="55"/>
-      <c r="AV32" s="113"/>
+      <c r="AV32" s="114"/>
       <c r="AW32" s="15">
         <v>2</v>
       </c>
@@ -25822,7 +25816,7 @@
         <v/>
       </c>
       <c r="BP32" s="55"/>
-      <c r="BQ32" s="113"/>
+      <c r="BQ32" s="114"/>
       <c r="BR32" s="15">
         <v>2</v>
       </c>
@@ -25879,7 +25873,7 @@
         <v>MN1</v>
       </c>
       <c r="CG32" s="55"/>
-      <c r="CH32" s="113"/>
+      <c r="CH32" s="114"/>
       <c r="CI32" s="15">
         <v>2</v>
       </c>
@@ -25956,7 +25950,7 @@
         <v>0</v>
       </c>
       <c r="DG32" s="66"/>
-      <c r="DH32" s="113"/>
+      <c r="DH32" s="114"/>
       <c r="DI32" s="15">
         <v>2</v>
       </c>
@@ -26035,7 +26029,7 @@
     </row>
     <row r="33" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E33" s="22"/>
-      <c r="F33" s="113"/>
+      <c r="F33" s="114"/>
       <c r="G33" s="15">
         <v>3</v>
       </c>
@@ -26112,7 +26106,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="22"/>
-      <c r="AA33" s="113"/>
+      <c r="AA33" s="114"/>
       <c r="AB33" s="15">
         <v>3</v>
       </c>
@@ -26189,7 +26183,7 @@
         <v/>
       </c>
       <c r="AU33" s="55"/>
-      <c r="AV33" s="113"/>
+      <c r="AV33" s="114"/>
       <c r="AW33" s="15">
         <v>3</v>
       </c>
@@ -26266,7 +26260,7 @@
         <v/>
       </c>
       <c r="BP33" s="55"/>
-      <c r="BQ33" s="113"/>
+      <c r="BQ33" s="114"/>
       <c r="BR33" s="15">
         <v>3</v>
       </c>
@@ -26323,7 +26317,7 @@
         <v>Trang</v>
       </c>
       <c r="CG33" s="55"/>
-      <c r="CH33" s="113"/>
+      <c r="CH33" s="114"/>
       <c r="CI33" s="15">
         <v>3</v>
       </c>
@@ -26400,7 +26394,7 @@
         <v>0</v>
       </c>
       <c r="DG33" s="66"/>
-      <c r="DH33" s="113"/>
+      <c r="DH33" s="114"/>
       <c r="DI33" s="15">
         <v>3</v>
       </c>
@@ -26479,7 +26473,7 @@
     </row>
     <row r="34" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E34" s="22"/>
-      <c r="F34" s="113"/>
+      <c r="F34" s="114"/>
       <c r="G34" s="15">
         <v>4</v>
       </c>
@@ -26543,9 +26537,9 @@
         <f>TKB_LOP_SC!AL19</f>
         <v>0</v>
       </c>
-      <c r="W34" s="2" t="str">
+      <c r="W34" s="2">
         <f>TKB_LOP_SC!AN19</f>
-        <v>GVVN - Linh</v>
+        <v>0</v>
       </c>
       <c r="X34" s="2">
         <f>TKB_LOP_SC!AP19</f>
@@ -26556,7 +26550,7 @@
         <v>GVNN - Aziz, Phượng</v>
       </c>
       <c r="Z34" s="22"/>
-      <c r="AA34" s="113"/>
+      <c r="AA34" s="114"/>
       <c r="AB34" s="15">
         <v>4</v>
       </c>
@@ -26633,7 +26627,7 @@
         <v/>
       </c>
       <c r="AU34" s="55"/>
-      <c r="AV34" s="113"/>
+      <c r="AV34" s="114"/>
       <c r="AW34" s="15">
         <v>4</v>
       </c>
@@ -26699,7 +26693,7 @@
       </c>
       <c r="BM34" s="29" t="str">
         <f t="shared" si="30"/>
-        <v>Linh</v>
+        <v/>
       </c>
       <c r="BN34" s="29" t="str">
         <f t="shared" si="31"/>
@@ -26710,7 +26704,7 @@
         <v>Aziz, Phượng</v>
       </c>
       <c r="BP34" s="55"/>
-      <c r="BQ34" s="113"/>
+      <c r="BQ34" s="114"/>
       <c r="BR34" s="15">
         <v>4</v>
       </c>
@@ -26767,7 +26761,7 @@
         <v>MN1</v>
       </c>
       <c r="CG34" s="55"/>
-      <c r="CH34" s="113"/>
+      <c r="CH34" s="114"/>
       <c r="CI34" s="15">
         <v>4</v>
       </c>
@@ -26844,7 +26838,7 @@
         <v>0</v>
       </c>
       <c r="DG34" s="66"/>
-      <c r="DH34" s="113"/>
+      <c r="DH34" s="114"/>
       <c r="DI34" s="15">
         <v>4</v>
       </c>
@@ -26923,7 +26917,7 @@
     </row>
     <row r="35" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E35" s="22"/>
-      <c r="F35" s="114"/>
+      <c r="F35" s="115"/>
       <c r="G35" s="16">
         <v>5</v>
       </c>
@@ -27000,7 +26994,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="22"/>
-      <c r="AA35" s="114"/>
+      <c r="AA35" s="115"/>
       <c r="AB35" s="16">
         <v>5</v>
       </c>
@@ -27077,7 +27071,7 @@
         <v/>
       </c>
       <c r="AU35" s="55"/>
-      <c r="AV35" s="114"/>
+      <c r="AV35" s="115"/>
       <c r="AW35" s="16">
         <v>5</v>
       </c>
@@ -27154,7 +27148,7 @@
         <v/>
       </c>
       <c r="BP35" s="55"/>
-      <c r="BQ35" s="114"/>
+      <c r="BQ35" s="115"/>
       <c r="BR35" s="16">
         <v>5</v>
       </c>
@@ -27211,7 +27205,7 @@
         <v/>
       </c>
       <c r="CG35" s="55"/>
-      <c r="CH35" s="114"/>
+      <c r="CH35" s="115"/>
       <c r="CI35" s="16">
         <v>5</v>
       </c>
@@ -27288,7 +27282,7 @@
         <v/>
       </c>
       <c r="DG35" s="66"/>
-      <c r="DH35" s="114"/>
+      <c r="DH35" s="115"/>
       <c r="DI35" s="16">
         <v>5</v>
       </c>
@@ -27366,10 +27360,10 @@
       </c>
     </row>
     <row r="36" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E36" s="109">
+      <c r="E36" s="116">
         <v>5</v>
       </c>
-      <c r="F36" s="112" t="s">
+      <c r="F36" s="113" t="s">
         <v>3</v>
       </c>
       <c r="G36" s="10">
@@ -27447,10 +27441,10 @@
         <f>TKB_LOP_SC!AQ21</f>
         <v>0</v>
       </c>
-      <c r="Z36" s="109">
+      <c r="Z36" s="116">
         <v>5</v>
       </c>
-      <c r="AA36" s="112" t="s">
+      <c r="AA36" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AB36" s="10">
@@ -27528,10 +27522,10 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU36" s="109">
+      <c r="AU36" s="116">
         <v>5</v>
       </c>
-      <c r="AV36" s="112" t="s">
+      <c r="AV36" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AW36" s="10">
@@ -27609,10 +27603,10 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP36" s="109">
+      <c r="BP36" s="116">
         <v>5</v>
       </c>
-      <c r="BQ36" s="112" t="s">
+      <c r="BQ36" s="113" t="s">
         <v>3</v>
       </c>
       <c r="BR36" s="10">
@@ -27670,10 +27664,10 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG36" s="109">
+      <c r="CG36" s="116">
         <v>5</v>
       </c>
-      <c r="CH36" s="112" t="s">
+      <c r="CH36" s="113" t="s">
         <v>3</v>
       </c>
       <c r="CI36" s="10">
@@ -27751,10 +27745,10 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG36" s="109">
+      <c r="DG36" s="116">
         <v>5</v>
       </c>
-      <c r="DH36" s="112" t="s">
+      <c r="DH36" s="113" t="s">
         <v>3</v>
       </c>
       <c r="DI36" s="10">
@@ -27834,8 +27828,8 @@
       </c>
     </row>
     <row r="37" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E37" s="110"/>
-      <c r="F37" s="113"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="114"/>
       <c r="G37" s="15">
         <v>2</v>
       </c>
@@ -27911,8 +27905,8 @@
         <f>TKB_LOP_SC!AQ22</f>
         <v>0</v>
       </c>
-      <c r="Z37" s="110"/>
-      <c r="AA37" s="113"/>
+      <c r="Z37" s="117"/>
+      <c r="AA37" s="114"/>
       <c r="AB37" s="15">
         <v>2</v>
       </c>
@@ -27988,8 +27982,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU37" s="110"/>
-      <c r="AV37" s="113"/>
+      <c r="AU37" s="117"/>
+      <c r="AV37" s="114"/>
       <c r="AW37" s="15">
         <v>2</v>
       </c>
@@ -28065,8 +28059,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP37" s="110"/>
-      <c r="BQ37" s="113"/>
+      <c r="BP37" s="117"/>
+      <c r="BQ37" s="114"/>
       <c r="BR37" s="15">
         <v>2</v>
       </c>
@@ -28122,8 +28116,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG37" s="110"/>
-      <c r="CH37" s="113"/>
+      <c r="CG37" s="117"/>
+      <c r="CH37" s="114"/>
       <c r="CI37" s="15">
         <v>2</v>
       </c>
@@ -28199,8 +28193,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG37" s="110"/>
-      <c r="DH37" s="113"/>
+      <c r="DG37" s="117"/>
+      <c r="DH37" s="114"/>
       <c r="DI37" s="15">
         <v>2</v>
       </c>
@@ -28278,8 +28272,8 @@
       </c>
     </row>
     <row r="38" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="110"/>
-      <c r="F38" s="113"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="114"/>
       <c r="G38" s="15">
         <v>3</v>
       </c>
@@ -28339,9 +28333,9 @@
         <f>TKB_LOP_SC!AI23</f>
         <v>GVVN - Trang</v>
       </c>
-      <c r="V38" s="2" t="str">
+      <c r="V38" s="2">
         <f>TKB_LOP_SC!AK23</f>
-        <v>GVVN - Linh</v>
+        <v>0</v>
       </c>
       <c r="W38" s="2">
         <f>TKB_LOP_SC!AM23</f>
@@ -28351,12 +28345,12 @@
         <f>TKB_LOP_SC!AO23</f>
         <v>0</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y38" s="2" t="str">
         <f>TKB_LOP_SC!AQ23</f>
-        <v>0</v>
-      </c>
-      <c r="Z38" s="110"/>
-      <c r="AA38" s="113"/>
+        <v>GVVN - Linh</v>
+      </c>
+      <c r="Z38" s="117"/>
+      <c r="AA38" s="114"/>
       <c r="AB38" s="15">
         <v>3</v>
       </c>
@@ -28432,8 +28426,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU38" s="110"/>
-      <c r="AV38" s="113"/>
+      <c r="AU38" s="117"/>
+      <c r="AV38" s="114"/>
       <c r="AW38" s="15">
         <v>3</v>
       </c>
@@ -28495,7 +28489,7 @@
       </c>
       <c r="BL38" s="29" t="str">
         <f t="shared" si="29"/>
-        <v>Linh</v>
+        <v/>
       </c>
       <c r="BM38" s="29" t="str">
         <f t="shared" si="30"/>
@@ -28507,10 +28501,10 @@
       </c>
       <c r="BO38" s="29" t="str">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BP38" s="110"/>
-      <c r="BQ38" s="113"/>
+        <v>Linh</v>
+      </c>
+      <c r="BP38" s="117"/>
+      <c r="BQ38" s="114"/>
       <c r="BR38" s="15">
         <v>3</v>
       </c>
@@ -28566,8 +28560,8 @@
         <f t="shared" si="44"/>
         <v>Trang</v>
       </c>
-      <c r="CG38" s="110"/>
-      <c r="CH38" s="113"/>
+      <c r="CG38" s="117"/>
+      <c r="CH38" s="114"/>
       <c r="CI38" s="15">
         <v>3</v>
       </c>
@@ -28643,8 +28637,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG38" s="110"/>
-      <c r="DH38" s="113"/>
+      <c r="DG38" s="117"/>
+      <c r="DH38" s="114"/>
       <c r="DI38" s="15">
         <v>3</v>
       </c>
@@ -28722,8 +28716,8 @@
       </c>
     </row>
     <row r="39" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E39" s="110"/>
-      <c r="F39" s="113"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="114"/>
       <c r="G39" s="15">
         <v>4</v>
       </c>
@@ -28799,8 +28793,8 @@
         <f>TKB_LOP_SC!AQ24</f>
         <v>0</v>
       </c>
-      <c r="Z39" s="110"/>
-      <c r="AA39" s="113"/>
+      <c r="Z39" s="117"/>
+      <c r="AA39" s="114"/>
       <c r="AB39" s="15">
         <v>4</v>
       </c>
@@ -28876,8 +28870,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU39" s="110"/>
-      <c r="AV39" s="113"/>
+      <c r="AU39" s="117"/>
+      <c r="AV39" s="114"/>
       <c r="AW39" s="15">
         <v>4</v>
       </c>
@@ -28953,8 +28947,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP39" s="110"/>
-      <c r="BQ39" s="113"/>
+      <c r="BP39" s="117"/>
+      <c r="BQ39" s="114"/>
       <c r="BR39" s="15">
         <v>4</v>
       </c>
@@ -29010,8 +29004,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG39" s="110"/>
-      <c r="CH39" s="113"/>
+      <c r="CG39" s="117"/>
+      <c r="CH39" s="114"/>
       <c r="CI39" s="15">
         <v>4</v>
       </c>
@@ -29087,8 +29081,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG39" s="110"/>
-      <c r="DH39" s="113"/>
+      <c r="DG39" s="117"/>
+      <c r="DH39" s="114"/>
       <c r="DI39" s="15">
         <v>4</v>
       </c>
@@ -29166,8 +29160,8 @@
       </c>
     </row>
     <row r="40" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E40" s="111"/>
-      <c r="F40" s="114"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="115"/>
       <c r="G40" s="16">
         <v>5</v>
       </c>
@@ -29243,8 +29237,8 @@
         <f>TKB_LOP_SC!AQ25</f>
         <v>0</v>
       </c>
-      <c r="Z40" s="111"/>
-      <c r="AA40" s="114"/>
+      <c r="Z40" s="118"/>
+      <c r="AA40" s="115"/>
       <c r="AB40" s="16">
         <v>5</v>
       </c>
@@ -29320,8 +29314,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU40" s="111"/>
-      <c r="AV40" s="114"/>
+      <c r="AU40" s="118"/>
+      <c r="AV40" s="115"/>
       <c r="AW40" s="16">
         <v>5</v>
       </c>
@@ -29397,8 +29391,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP40" s="111"/>
-      <c r="BQ40" s="114"/>
+      <c r="BP40" s="118"/>
+      <c r="BQ40" s="115"/>
       <c r="BR40" s="16">
         <v>5</v>
       </c>
@@ -29454,8 +29448,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG40" s="111"/>
-      <c r="CH40" s="114"/>
+      <c r="CG40" s="118"/>
+      <c r="CH40" s="115"/>
       <c r="CI40" s="16">
         <v>5</v>
       </c>
@@ -29531,8 +29525,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG40" s="111"/>
-      <c r="DH40" s="114"/>
+      <c r="DG40" s="118"/>
+      <c r="DH40" s="115"/>
       <c r="DI40" s="16">
         <v>5</v>
       </c>
@@ -29611,7 +29605,7 @@
     </row>
     <row r="41" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E41" s="22"/>
-      <c r="F41" s="112" t="s">
+      <c r="F41" s="113" t="s">
         <v>4</v>
       </c>
       <c r="G41" s="10">
@@ -29690,7 +29684,7 @@
         <v>0</v>
       </c>
       <c r="Z41" s="22"/>
-      <c r="AA41" s="112" t="s">
+      <c r="AA41" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AB41" s="10">
@@ -29769,7 +29763,7 @@
         <v/>
       </c>
       <c r="AU41" s="55"/>
-      <c r="AV41" s="112" t="s">
+      <c r="AV41" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AW41" s="10">
@@ -29848,7 +29842,7 @@
         <v/>
       </c>
       <c r="BP41" s="55"/>
-      <c r="BQ41" s="112" t="s">
+      <c r="BQ41" s="113" t="s">
         <v>4</v>
       </c>
       <c r="BR41" s="10">
@@ -29907,7 +29901,7 @@
         <v>MN1</v>
       </c>
       <c r="CG41" s="55"/>
-      <c r="CH41" s="112" t="s">
+      <c r="CH41" s="113" t="s">
         <v>4</v>
       </c>
       <c r="CI41" s="10">
@@ -29986,7 +29980,7 @@
         <v>0</v>
       </c>
       <c r="DG41" s="66"/>
-      <c r="DH41" s="112" t="s">
+      <c r="DH41" s="113" t="s">
         <v>4</v>
       </c>
       <c r="DI41" s="10">
@@ -30067,7 +30061,7 @@
     </row>
     <row r="42" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E42" s="22"/>
-      <c r="F42" s="113"/>
+      <c r="F42" s="114"/>
       <c r="G42" s="15">
         <v>2</v>
       </c>
@@ -30144,7 +30138,7 @@
         <v>0</v>
       </c>
       <c r="Z42" s="22"/>
-      <c r="AA42" s="113"/>
+      <c r="AA42" s="114"/>
       <c r="AB42" s="15">
         <v>2</v>
       </c>
@@ -30221,7 +30215,7 @@
         <v/>
       </c>
       <c r="AU42" s="55"/>
-      <c r="AV42" s="113"/>
+      <c r="AV42" s="114"/>
       <c r="AW42" s="15">
         <v>2</v>
       </c>
@@ -30298,7 +30292,7 @@
         <v/>
       </c>
       <c r="BP42" s="55"/>
-      <c r="BQ42" s="113"/>
+      <c r="BQ42" s="114"/>
       <c r="BR42" s="15">
         <v>2</v>
       </c>
@@ -30355,7 +30349,7 @@
         <v>Trang</v>
       </c>
       <c r="CG42" s="55"/>
-      <c r="CH42" s="113"/>
+      <c r="CH42" s="114"/>
       <c r="CI42" s="15">
         <v>2</v>
       </c>
@@ -30432,7 +30426,7 @@
         <v>0</v>
       </c>
       <c r="DG42" s="66"/>
-      <c r="DH42" s="113"/>
+      <c r="DH42" s="114"/>
       <c r="DI42" s="15">
         <v>2</v>
       </c>
@@ -30511,7 +30505,7 @@
     </row>
     <row r="43" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="22"/>
-      <c r="F43" s="113"/>
+      <c r="F43" s="114"/>
       <c r="G43" s="15">
         <v>3</v>
       </c>
@@ -30588,7 +30582,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="22"/>
-      <c r="AA43" s="113"/>
+      <c r="AA43" s="114"/>
       <c r="AB43" s="15">
         <v>3</v>
       </c>
@@ -30665,7 +30659,7 @@
         <v/>
       </c>
       <c r="AU43" s="55"/>
-      <c r="AV43" s="113"/>
+      <c r="AV43" s="114"/>
       <c r="AW43" s="15">
         <v>3</v>
       </c>
@@ -30742,7 +30736,7 @@
         <v/>
       </c>
       <c r="BP43" s="55"/>
-      <c r="BQ43" s="113"/>
+      <c r="BQ43" s="114"/>
       <c r="BR43" s="15">
         <v>3</v>
       </c>
@@ -30799,7 +30793,7 @@
         <v>Nguyên</v>
       </c>
       <c r="CG43" s="55"/>
-      <c r="CH43" s="113"/>
+      <c r="CH43" s="114"/>
       <c r="CI43" s="15">
         <v>3</v>
       </c>
@@ -30876,7 +30870,7 @@
         <v>0</v>
       </c>
       <c r="DG43" s="66"/>
-      <c r="DH43" s="113"/>
+      <c r="DH43" s="114"/>
       <c r="DI43" s="15">
         <v>3</v>
       </c>
@@ -30955,7 +30949,7 @@
     </row>
     <row r="44" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E44" s="22"/>
-      <c r="F44" s="113"/>
+      <c r="F44" s="114"/>
       <c r="G44" s="15">
         <v>4</v>
       </c>
@@ -31032,7 +31026,7 @@
         <v>GVVN - Linh</v>
       </c>
       <c r="Z44" s="22"/>
-      <c r="AA44" s="113"/>
+      <c r="AA44" s="114"/>
       <c r="AB44" s="15">
         <v>4</v>
       </c>
@@ -31109,7 +31103,7 @@
         <v/>
       </c>
       <c r="AU44" s="55"/>
-      <c r="AV44" s="113"/>
+      <c r="AV44" s="114"/>
       <c r="AW44" s="15">
         <v>4</v>
       </c>
@@ -31186,7 +31180,7 @@
         <v>Linh</v>
       </c>
       <c r="BP44" s="55"/>
-      <c r="BQ44" s="113"/>
+      <c r="BQ44" s="114"/>
       <c r="BR44" s="15">
         <v>4</v>
       </c>
@@ -31243,7 +31237,7 @@
         <v>MN1</v>
       </c>
       <c r="CG44" s="55"/>
-      <c r="CH44" s="113"/>
+      <c r="CH44" s="114"/>
       <c r="CI44" s="15">
         <v>4</v>
       </c>
@@ -31320,7 +31314,7 @@
         <v>0</v>
       </c>
       <c r="DG44" s="66"/>
-      <c r="DH44" s="113"/>
+      <c r="DH44" s="114"/>
       <c r="DI44" s="15">
         <v>4</v>
       </c>
@@ -31399,7 +31393,7 @@
     </row>
     <row r="45" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E45" s="22"/>
-      <c r="F45" s="114"/>
+      <c r="F45" s="115"/>
       <c r="G45" s="16">
         <v>5</v>
       </c>
@@ -31476,7 +31470,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="22"/>
-      <c r="AA45" s="114"/>
+      <c r="AA45" s="115"/>
       <c r="AB45" s="16">
         <v>5</v>
       </c>
@@ -31553,7 +31547,7 @@
         <v/>
       </c>
       <c r="AU45" s="55"/>
-      <c r="AV45" s="114"/>
+      <c r="AV45" s="115"/>
       <c r="AW45" s="16">
         <v>5</v>
       </c>
@@ -31630,7 +31624,7 @@
         <v/>
       </c>
       <c r="BP45" s="55"/>
-      <c r="BQ45" s="114"/>
+      <c r="BQ45" s="115"/>
       <c r="BR45" s="16">
         <v>5</v>
       </c>
@@ -31687,7 +31681,7 @@
         <v/>
       </c>
       <c r="CG45" s="55"/>
-      <c r="CH45" s="114"/>
+      <c r="CH45" s="115"/>
       <c r="CI45" s="16">
         <v>5</v>
       </c>
@@ -31764,7 +31758,7 @@
         <v/>
       </c>
       <c r="DG45" s="66"/>
-      <c r="DH45" s="114"/>
+      <c r="DH45" s="115"/>
       <c r="DI45" s="16">
         <v>5</v>
       </c>
@@ -31842,10 +31836,10 @@
       </c>
     </row>
     <row r="46" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E46" s="109">
+      <c r="E46" s="116">
         <v>6</v>
       </c>
-      <c r="F46" s="112" t="s">
+      <c r="F46" s="113" t="s">
         <v>3</v>
       </c>
       <c r="G46" s="10">
@@ -31923,10 +31917,10 @@
         <f>TKB_LOP_SC!AQ26</f>
         <v>GVVN - Linh</v>
       </c>
-      <c r="Z46" s="109">
+      <c r="Z46" s="116">
         <v>6</v>
       </c>
-      <c r="AA46" s="112" t="s">
+      <c r="AA46" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AB46" s="10">
@@ -32004,10 +31998,10 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU46" s="109">
+      <c r="AU46" s="116">
         <v>6</v>
       </c>
-      <c r="AV46" s="112" t="s">
+      <c r="AV46" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AW46" s="10">
@@ -32085,10 +32079,10 @@
         <f t="shared" si="32"/>
         <v>Linh</v>
       </c>
-      <c r="BP46" s="109">
+      <c r="BP46" s="116">
         <v>6</v>
       </c>
-      <c r="BQ46" s="112" t="s">
+      <c r="BQ46" s="113" t="s">
         <v>3</v>
       </c>
       <c r="BR46" s="10">
@@ -32146,10 +32140,10 @@
         <f t="shared" si="44"/>
         <v>Trang ÂN</v>
       </c>
-      <c r="CG46" s="109">
+      <c r="CG46" s="116">
         <v>6</v>
       </c>
-      <c r="CH46" s="112" t="s">
+      <c r="CH46" s="113" t="s">
         <v>3</v>
       </c>
       <c r="CI46" s="10">
@@ -32227,10 +32221,10 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG46" s="109">
+      <c r="DG46" s="116">
         <v>6</v>
       </c>
-      <c r="DH46" s="112" t="s">
+      <c r="DH46" s="113" t="s">
         <v>3</v>
       </c>
       <c r="DI46" s="10">
@@ -32310,8 +32304,8 @@
       </c>
     </row>
     <row r="47" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E47" s="110"/>
-      <c r="F47" s="113"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="114"/>
       <c r="G47" s="15">
         <v>2</v>
       </c>
@@ -32387,8 +32381,8 @@
         <f>TKB_LOP_SC!AQ27</f>
         <v>0</v>
       </c>
-      <c r="Z47" s="110"/>
-      <c r="AA47" s="113"/>
+      <c r="Z47" s="117"/>
+      <c r="AA47" s="114"/>
       <c r="AB47" s="15">
         <v>2</v>
       </c>
@@ -32464,8 +32458,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU47" s="110"/>
-      <c r="AV47" s="113"/>
+      <c r="AU47" s="117"/>
+      <c r="AV47" s="114"/>
       <c r="AW47" s="15">
         <v>2</v>
       </c>
@@ -32541,8 +32535,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP47" s="110"/>
-      <c r="BQ47" s="113"/>
+      <c r="BP47" s="117"/>
+      <c r="BQ47" s="114"/>
       <c r="BR47" s="15">
         <v>2</v>
       </c>
@@ -32598,8 +32592,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG47" s="110"/>
-      <c r="CH47" s="113"/>
+      <c r="CG47" s="117"/>
+      <c r="CH47" s="114"/>
       <c r="CI47" s="15">
         <v>2</v>
       </c>
@@ -32675,8 +32669,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG47" s="110"/>
-      <c r="DH47" s="113"/>
+      <c r="DG47" s="117"/>
+      <c r="DH47" s="114"/>
       <c r="DI47" s="15">
         <v>2</v>
       </c>
@@ -32754,8 +32748,8 @@
       </c>
     </row>
     <row r="48" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E48" s="110"/>
-      <c r="F48" s="113"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="114"/>
       <c r="G48" s="15">
         <v>3</v>
       </c>
@@ -32815,9 +32809,9 @@
         <f>TKB_LOP_SC!AI28</f>
         <v>TViệt - MN2</v>
       </c>
-      <c r="V48" s="2">
+      <c r="V48" s="2" t="str">
         <f>TKB_LOP_SC!AK28</f>
-        <v>0</v>
+        <v>GVVN - Linh</v>
       </c>
       <c r="W48" s="2" t="str">
         <f>TKB_LOP_SC!AM28</f>
@@ -32831,8 +32825,8 @@
         <f>TKB_LOP_SC!AQ28</f>
         <v>0</v>
       </c>
-      <c r="Z48" s="110"/>
-      <c r="AA48" s="113"/>
+      <c r="Z48" s="117"/>
+      <c r="AA48" s="114"/>
       <c r="AB48" s="15">
         <v>3</v>
       </c>
@@ -32908,8 +32902,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU48" s="110"/>
-      <c r="AV48" s="113"/>
+      <c r="AU48" s="117"/>
+      <c r="AV48" s="114"/>
       <c r="AW48" s="15">
         <v>3</v>
       </c>
@@ -32971,7 +32965,7 @@
       </c>
       <c r="BL48" s="29" t="str">
         <f t="shared" si="29"/>
-        <v/>
+        <v>Linh</v>
       </c>
       <c r="BM48" s="29" t="str">
         <f t="shared" si="30"/>
@@ -32985,8 +32979,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP48" s="110"/>
-      <c r="BQ48" s="113"/>
+      <c r="BP48" s="117"/>
+      <c r="BQ48" s="114"/>
       <c r="BR48" s="15">
         <v>3</v>
       </c>
@@ -33042,8 +33036,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG48" s="110"/>
-      <c r="CH48" s="113"/>
+      <c r="CG48" s="117"/>
+      <c r="CH48" s="114"/>
       <c r="CI48" s="15">
         <v>3</v>
       </c>
@@ -33119,8 +33113,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG48" s="110"/>
-      <c r="DH48" s="113"/>
+      <c r="DG48" s="117"/>
+      <c r="DH48" s="114"/>
       <c r="DI48" s="15">
         <v>3</v>
       </c>
@@ -33198,8 +33192,8 @@
       </c>
     </row>
     <row r="49" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E49" s="110"/>
-      <c r="F49" s="113"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="114"/>
       <c r="G49" s="15">
         <v>4</v>
       </c>
@@ -33275,8 +33269,8 @@
         <f>TKB_LOP_SC!AQ29</f>
         <v>0</v>
       </c>
-      <c r="Z49" s="110"/>
-      <c r="AA49" s="113"/>
+      <c r="Z49" s="117"/>
+      <c r="AA49" s="114"/>
       <c r="AB49" s="15">
         <v>4</v>
       </c>
@@ -33352,8 +33346,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU49" s="110"/>
-      <c r="AV49" s="113"/>
+      <c r="AU49" s="117"/>
+      <c r="AV49" s="114"/>
       <c r="AW49" s="15">
         <v>4</v>
       </c>
@@ -33429,8 +33423,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP49" s="110"/>
-      <c r="BQ49" s="113"/>
+      <c r="BP49" s="117"/>
+      <c r="BQ49" s="114"/>
       <c r="BR49" s="15">
         <v>4</v>
       </c>
@@ -33486,8 +33480,8 @@
         <f t="shared" si="44"/>
         <v>Huyền</v>
       </c>
-      <c r="CG49" s="110"/>
-      <c r="CH49" s="113"/>
+      <c r="CG49" s="117"/>
+      <c r="CH49" s="114"/>
       <c r="CI49" s="15">
         <v>4</v>
       </c>
@@ -33563,8 +33557,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG49" s="110"/>
-      <c r="DH49" s="113"/>
+      <c r="DG49" s="117"/>
+      <c r="DH49" s="114"/>
       <c r="DI49" s="15">
         <v>4</v>
       </c>
@@ -33642,8 +33636,8 @@
       </c>
     </row>
     <row r="50" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E50" s="111"/>
-      <c r="F50" s="114"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="115"/>
       <c r="G50" s="16">
         <v>5</v>
       </c>
@@ -33691,8 +33685,8 @@
         <f>TKB_LOP_SC!AQ30</f>
         <v>0</v>
       </c>
-      <c r="Z50" s="111"/>
-      <c r="AA50" s="114"/>
+      <c r="Z50" s="118"/>
+      <c r="AA50" s="115"/>
       <c r="AB50" s="16">
         <v>5</v>
       </c>
@@ -33768,8 +33762,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU50" s="111"/>
-      <c r="AV50" s="114"/>
+      <c r="AU50" s="118"/>
+      <c r="AV50" s="115"/>
       <c r="AW50" s="16">
         <v>5</v>
       </c>
@@ -33845,8 +33839,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP50" s="111"/>
-      <c r="BQ50" s="114"/>
+      <c r="BP50" s="118"/>
+      <c r="BQ50" s="115"/>
       <c r="BR50" s="16">
         <v>5</v>
       </c>
@@ -33902,8 +33896,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG50" s="111"/>
-      <c r="CH50" s="114"/>
+      <c r="CG50" s="118"/>
+      <c r="CH50" s="115"/>
       <c r="CI50" s="16">
         <v>5</v>
       </c>
@@ -33979,8 +33973,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG50" s="111"/>
-      <c r="DH50" s="114"/>
+      <c r="DG50" s="118"/>
+      <c r="DH50" s="115"/>
       <c r="DI50" s="16">
         <v>5</v>
       </c>
@@ -34058,8 +34052,8 @@
       </c>
     </row>
     <row r="51" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E51" s="109"/>
-      <c r="F51" s="112" t="s">
+      <c r="E51" s="116"/>
+      <c r="F51" s="113" t="s">
         <v>4</v>
       </c>
       <c r="G51" s="10">
@@ -34137,8 +34131,8 @@
         <f>TKB_LOP_SC!AR26</f>
         <v>0</v>
       </c>
-      <c r="Z51" s="109"/>
-      <c r="AA51" s="112" t="s">
+      <c r="Z51" s="116"/>
+      <c r="AA51" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AB51" s="10">
@@ -34216,8 +34210,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU51" s="109"/>
-      <c r="AV51" s="112" t="s">
+      <c r="AU51" s="116"/>
+      <c r="AV51" s="113" t="s">
         <v>4</v>
       </c>
       <c r="AW51" s="10">
@@ -34295,8 +34289,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP51" s="109"/>
-      <c r="BQ51" s="112" t="s">
+      <c r="BP51" s="116"/>
+      <c r="BQ51" s="113" t="s">
         <v>4</v>
       </c>
       <c r="BR51" s="10">
@@ -34354,8 +34348,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG51" s="109"/>
-      <c r="CH51" s="112" t="s">
+      <c r="CG51" s="116"/>
+      <c r="CH51" s="113" t="s">
         <v>4</v>
       </c>
       <c r="CI51" s="10">
@@ -34433,8 +34427,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG51" s="109"/>
-      <c r="DH51" s="112" t="s">
+      <c r="DG51" s="116"/>
+      <c r="DH51" s="113" t="s">
         <v>4</v>
       </c>
       <c r="DI51" s="10">
@@ -34514,8 +34508,8 @@
       </c>
     </row>
     <row r="52" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E52" s="110"/>
-      <c r="F52" s="113"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="114"/>
       <c r="G52" s="15">
         <v>2</v>
       </c>
@@ -34591,8 +34585,8 @@
         <f>TKB_LOP_SC!AR27</f>
         <v>GVNN - Aziz, Phượng</v>
       </c>
-      <c r="Z52" s="110"/>
-      <c r="AA52" s="113"/>
+      <c r="Z52" s="117"/>
+      <c r="AA52" s="114"/>
       <c r="AB52" s="15">
         <v>2</v>
       </c>
@@ -34668,8 +34662,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU52" s="110"/>
-      <c r="AV52" s="113"/>
+      <c r="AU52" s="117"/>
+      <c r="AV52" s="114"/>
       <c r="AW52" s="15">
         <v>2</v>
       </c>
@@ -34745,8 +34739,8 @@
         <f t="shared" si="32"/>
         <v>Aziz, Phượng</v>
       </c>
-      <c r="BP52" s="110"/>
-      <c r="BQ52" s="113"/>
+      <c r="BP52" s="117"/>
+      <c r="BQ52" s="114"/>
       <c r="BR52" s="15">
         <v>2</v>
       </c>
@@ -34802,8 +34796,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG52" s="110"/>
-      <c r="CH52" s="113"/>
+      <c r="CG52" s="117"/>
+      <c r="CH52" s="114"/>
       <c r="CI52" s="15">
         <v>2</v>
       </c>
@@ -34879,8 +34873,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG52" s="110"/>
-      <c r="DH52" s="113"/>
+      <c r="DG52" s="117"/>
+      <c r="DH52" s="114"/>
       <c r="DI52" s="15">
         <v>2</v>
       </c>
@@ -34958,8 +34952,8 @@
       </c>
     </row>
     <row r="53" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E53" s="110"/>
-      <c r="F53" s="113"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="114"/>
       <c r="G53" s="15">
         <v>3</v>
       </c>
@@ -35019,9 +35013,9 @@
         <f>TKB_LOP_SC!AJ28</f>
         <v>Toán - MN2</v>
       </c>
-      <c r="V53" s="2" t="str">
+      <c r="V53" s="2">
         <f>TKB_LOP_SC!AL28</f>
-        <v>GVVN - Linh</v>
+        <v>0</v>
       </c>
       <c r="W53" s="2">
         <f>TKB_LOP_SC!AN28</f>
@@ -35031,12 +35025,12 @@
         <f>TKB_LOP_SC!AP28</f>
         <v>0</v>
       </c>
-      <c r="Y53" s="2">
+      <c r="Y53" s="2" t="str">
         <f>TKB_LOP_SC!AR28</f>
-        <v>0</v>
-      </c>
-      <c r="Z53" s="110"/>
-      <c r="AA53" s="113"/>
+        <v>GVVN - Linh</v>
+      </c>
+      <c r="Z53" s="117"/>
+      <c r="AA53" s="114"/>
       <c r="AB53" s="15">
         <v>3</v>
       </c>
@@ -35112,8 +35106,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU53" s="110"/>
-      <c r="AV53" s="113"/>
+      <c r="AU53" s="117"/>
+      <c r="AV53" s="114"/>
       <c r="AW53" s="15">
         <v>3</v>
       </c>
@@ -35175,7 +35169,7 @@
       </c>
       <c r="BL53" s="29" t="str">
         <f t="shared" si="29"/>
-        <v>Linh</v>
+        <v/>
       </c>
       <c r="BM53" s="29" t="str">
         <f t="shared" si="30"/>
@@ -35187,10 +35181,10 @@
       </c>
       <c r="BO53" s="29" t="str">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BP53" s="110"/>
-      <c r="BQ53" s="113"/>
+        <v>Linh</v>
+      </c>
+      <c r="BP53" s="117"/>
+      <c r="BQ53" s="114"/>
       <c r="BR53" s="15">
         <v>3</v>
       </c>
@@ -35246,8 +35240,8 @@
         <f t="shared" si="44"/>
         <v>MN1</v>
       </c>
-      <c r="CG53" s="110"/>
-      <c r="CH53" s="113"/>
+      <c r="CG53" s="117"/>
+      <c r="CH53" s="114"/>
       <c r="CI53" s="15">
         <v>3</v>
       </c>
@@ -35323,8 +35317,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG53" s="110"/>
-      <c r="DH53" s="113"/>
+      <c r="DG53" s="117"/>
+      <c r="DH53" s="114"/>
       <c r="DI53" s="15">
         <v>3</v>
       </c>
@@ -35402,8 +35396,8 @@
       </c>
     </row>
     <row r="54" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E54" s="110"/>
-      <c r="F54" s="113"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="114"/>
       <c r="G54" s="15">
         <v>4</v>
       </c>
@@ -35475,12 +35469,12 @@
         <f>TKB_LOP_SC!AP29</f>
         <v>0</v>
       </c>
-      <c r="Y54" s="2" t="str">
+      <c r="Y54" s="2">
         <f>TKB_LOP_SC!AR29</f>
-        <v>GVVN - Linh</v>
-      </c>
-      <c r="Z54" s="110"/>
-      <c r="AA54" s="113"/>
+        <v>0</v>
+      </c>
+      <c r="Z54" s="117"/>
+      <c r="AA54" s="114"/>
       <c r="AB54" s="15">
         <v>4</v>
       </c>
@@ -35556,8 +35550,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU54" s="110"/>
-      <c r="AV54" s="113"/>
+      <c r="AU54" s="117"/>
+      <c r="AV54" s="114"/>
       <c r="AW54" s="15">
         <v>4</v>
       </c>
@@ -35631,10 +35625,10 @@
       </c>
       <c r="BO54" s="29" t="str">
         <f t="shared" si="32"/>
-        <v>Linh</v>
-      </c>
-      <c r="BP54" s="110"/>
-      <c r="BQ54" s="113"/>
+        <v/>
+      </c>
+      <c r="BP54" s="117"/>
+      <c r="BQ54" s="114"/>
       <c r="BR54" s="15">
         <v>4</v>
       </c>
@@ -35690,8 +35684,8 @@
         <f t="shared" si="44"/>
         <v>Huyền</v>
       </c>
-      <c r="CG54" s="110"/>
-      <c r="CH54" s="113"/>
+      <c r="CG54" s="117"/>
+      <c r="CH54" s="114"/>
       <c r="CI54" s="15">
         <v>4</v>
       </c>
@@ -35767,8 +35761,8 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="DG54" s="110"/>
-      <c r="DH54" s="113"/>
+      <c r="DG54" s="117"/>
+      <c r="DH54" s="114"/>
       <c r="DI54" s="15">
         <v>4</v>
       </c>
@@ -35846,8 +35840,8 @@
       </c>
     </row>
     <row r="55" spans="5:131" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E55" s="111"/>
-      <c r="F55" s="114"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="115"/>
       <c r="G55" s="16">
         <v>5</v>
       </c>
@@ -35923,8 +35917,8 @@
         <f>TKB_LOP_SC!AR30</f>
         <v>0</v>
       </c>
-      <c r="Z55" s="111"/>
-      <c r="AA55" s="114"/>
+      <c r="Z55" s="118"/>
+      <c r="AA55" s="115"/>
       <c r="AB55" s="16">
         <v>5</v>
       </c>
@@ -36000,8 +35994,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU55" s="111"/>
-      <c r="AV55" s="114"/>
+      <c r="AU55" s="118"/>
+      <c r="AV55" s="115"/>
       <c r="AW55" s="16">
         <v>5</v>
       </c>
@@ -36077,8 +36071,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP55" s="111"/>
-      <c r="BQ55" s="114"/>
+      <c r="BP55" s="118"/>
+      <c r="BQ55" s="115"/>
       <c r="BR55" s="16">
         <v>5</v>
       </c>
@@ -36134,8 +36128,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG55" s="111"/>
-      <c r="CH55" s="114"/>
+      <c r="CG55" s="118"/>
+      <c r="CH55" s="115"/>
       <c r="CI55" s="16">
         <v>5</v>
       </c>
@@ -36211,8 +36205,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG55" s="111"/>
-      <c r="DH55" s="114"/>
+      <c r="DG55" s="118"/>
+      <c r="DH55" s="115"/>
       <c r="DI55" s="16">
         <v>5</v>
       </c>
@@ -36290,10 +36284,10 @@
       </c>
     </row>
     <row r="56" spans="5:131" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E56" s="109">
+      <c r="E56" s="116">
         <v>7</v>
       </c>
-      <c r="F56" s="112" t="s">
+      <c r="F56" s="113" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="10">
@@ -36311,10 +36305,10 @@
       <c r="Q56" s="11"/>
       <c r="R56" s="20"/>
       <c r="S56" s="21"/>
-      <c r="Z56" s="109">
+      <c r="Z56" s="116">
         <v>7</v>
       </c>
-      <c r="AA56" s="112" t="s">
+      <c r="AA56" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AB56" s="10">
@@ -36392,10 +36386,10 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU56" s="109">
+      <c r="AU56" s="116">
         <v>7</v>
       </c>
-      <c r="AV56" s="112" t="s">
+      <c r="AV56" s="113" t="s">
         <v>3</v>
       </c>
       <c r="AW56" s="10">
@@ -36473,10 +36467,10 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP56" s="109">
+      <c r="BP56" s="116">
         <v>7</v>
       </c>
-      <c r="BQ56" s="112" t="s">
+      <c r="BQ56" s="113" t="s">
         <v>3</v>
       </c>
       <c r="BR56" s="10">
@@ -36534,10 +36528,10 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG56" s="109">
+      <c r="CG56" s="116">
         <v>7</v>
       </c>
-      <c r="CH56" s="112" t="s">
+      <c r="CH56" s="113" t="s">
         <v>3</v>
       </c>
       <c r="CI56" s="10">
@@ -36615,10 +36609,10 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG56" s="109">
+      <c r="DG56" s="116">
         <v>7</v>
       </c>
-      <c r="DH56" s="112" t="s">
+      <c r="DH56" s="113" t="s">
         <v>3</v>
       </c>
       <c r="DI56" s="10">
@@ -36698,8 +36692,8 @@
       </c>
     </row>
     <row r="57" spans="5:131" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E57" s="110"/>
-      <c r="F57" s="113"/>
+      <c r="E57" s="117"/>
+      <c r="F57" s="114"/>
       <c r="G57" s="15">
         <v>2</v>
       </c>
@@ -36715,8 +36709,8 @@
       <c r="Q57" s="12"/>
       <c r="R57" s="13"/>
       <c r="S57" s="14"/>
-      <c r="Z57" s="110"/>
-      <c r="AA57" s="113"/>
+      <c r="Z57" s="117"/>
+      <c r="AA57" s="114"/>
       <c r="AB57" s="15">
         <v>2</v>
       </c>
@@ -36792,8 +36786,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU57" s="110"/>
-      <c r="AV57" s="113"/>
+      <c r="AU57" s="117"/>
+      <c r="AV57" s="114"/>
       <c r="AW57" s="15">
         <v>2</v>
       </c>
@@ -36869,8 +36863,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP57" s="110"/>
-      <c r="BQ57" s="113"/>
+      <c r="BP57" s="117"/>
+      <c r="BQ57" s="114"/>
       <c r="BR57" s="15">
         <v>2</v>
       </c>
@@ -36926,8 +36920,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG57" s="110"/>
-      <c r="CH57" s="113"/>
+      <c r="CG57" s="117"/>
+      <c r="CH57" s="114"/>
       <c r="CI57" s="15">
         <v>2</v>
       </c>
@@ -37003,8 +36997,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG57" s="110"/>
-      <c r="DH57" s="113"/>
+      <c r="DG57" s="117"/>
+      <c r="DH57" s="114"/>
       <c r="DI57" s="15">
         <v>2</v>
       </c>
@@ -37082,8 +37076,8 @@
       </c>
     </row>
     <row r="58" spans="5:131" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E58" s="110"/>
-      <c r="F58" s="113"/>
+      <c r="E58" s="117"/>
+      <c r="F58" s="114"/>
       <c r="G58" s="15">
         <v>3</v>
       </c>
@@ -37099,8 +37093,8 @@
       <c r="Q58" s="12"/>
       <c r="R58" s="13"/>
       <c r="S58" s="14"/>
-      <c r="Z58" s="110"/>
-      <c r="AA58" s="113"/>
+      <c r="Z58" s="117"/>
+      <c r="AA58" s="114"/>
       <c r="AB58" s="15">
         <v>3</v>
       </c>
@@ -37176,8 +37170,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU58" s="110"/>
-      <c r="AV58" s="113"/>
+      <c r="AU58" s="117"/>
+      <c r="AV58" s="114"/>
       <c r="AW58" s="15">
         <v>3</v>
       </c>
@@ -37253,8 +37247,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP58" s="110"/>
-      <c r="BQ58" s="113"/>
+      <c r="BP58" s="117"/>
+      <c r="BQ58" s="114"/>
       <c r="BR58" s="15">
         <v>3</v>
       </c>
@@ -37310,8 +37304,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG58" s="110"/>
-      <c r="CH58" s="113"/>
+      <c r="CG58" s="117"/>
+      <c r="CH58" s="114"/>
       <c r="CI58" s="15">
         <v>3</v>
       </c>
@@ -37387,8 +37381,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG58" s="110"/>
-      <c r="DH58" s="113"/>
+      <c r="DG58" s="117"/>
+      <c r="DH58" s="114"/>
       <c r="DI58" s="15">
         <v>3</v>
       </c>
@@ -37466,8 +37460,8 @@
       </c>
     </row>
     <row r="59" spans="5:131" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E59" s="110"/>
-      <c r="F59" s="113"/>
+      <c r="E59" s="117"/>
+      <c r="F59" s="114"/>
       <c r="G59" s="15">
         <v>4</v>
       </c>
@@ -37483,8 +37477,8 @@
       <c r="Q59" s="12"/>
       <c r="R59" s="13"/>
       <c r="S59" s="14"/>
-      <c r="Z59" s="110"/>
-      <c r="AA59" s="113"/>
+      <c r="Z59" s="117"/>
+      <c r="AA59" s="114"/>
       <c r="AB59" s="15">
         <v>4</v>
       </c>
@@ -37560,8 +37554,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU59" s="110"/>
-      <c r="AV59" s="113"/>
+      <c r="AU59" s="117"/>
+      <c r="AV59" s="114"/>
       <c r="AW59" s="15">
         <v>4</v>
       </c>
@@ -37637,8 +37631,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP59" s="110"/>
-      <c r="BQ59" s="113"/>
+      <c r="BP59" s="117"/>
+      <c r="BQ59" s="114"/>
       <c r="BR59" s="15">
         <v>4</v>
       </c>
@@ -37694,8 +37688,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG59" s="110"/>
-      <c r="CH59" s="113"/>
+      <c r="CG59" s="117"/>
+      <c r="CH59" s="114"/>
       <c r="CI59" s="15">
         <v>4</v>
       </c>
@@ -37771,8 +37765,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG59" s="110"/>
-      <c r="DH59" s="113"/>
+      <c r="DG59" s="117"/>
+      <c r="DH59" s="114"/>
       <c r="DI59" s="15">
         <v>4</v>
       </c>
@@ -37850,8 +37844,8 @@
       </c>
     </row>
     <row r="60" spans="5:131" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E60" s="111"/>
-      <c r="F60" s="114"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="115"/>
       <c r="G60" s="16">
         <v>5</v>
       </c>
@@ -37867,8 +37861,8 @@
       <c r="Q60" s="17"/>
       <c r="R60" s="18"/>
       <c r="S60" s="19"/>
-      <c r="Z60" s="111"/>
-      <c r="AA60" s="114"/>
+      <c r="Z60" s="118"/>
+      <c r="AA60" s="115"/>
       <c r="AB60" s="16">
         <v>5</v>
       </c>
@@ -37944,8 +37938,8 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AU60" s="111"/>
-      <c r="AV60" s="114"/>
+      <c r="AU60" s="118"/>
+      <c r="AV60" s="115"/>
       <c r="AW60" s="16">
         <v>5</v>
       </c>
@@ -38021,8 +38015,8 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="BP60" s="111"/>
-      <c r="BQ60" s="114"/>
+      <c r="BP60" s="118"/>
+      <c r="BQ60" s="115"/>
       <c r="BR60" s="16">
         <v>5</v>
       </c>
@@ -38078,8 +38072,8 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="CG60" s="111"/>
-      <c r="CH60" s="114"/>
+      <c r="CG60" s="118"/>
+      <c r="CH60" s="115"/>
       <c r="CI60" s="16">
         <v>5</v>
       </c>
@@ -38155,8 +38149,8 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="DG60" s="111"/>
-      <c r="DH60" s="114"/>
+      <c r="DG60" s="118"/>
+      <c r="DH60" s="115"/>
       <c r="DI60" s="16">
         <v>5</v>
       </c>
@@ -39150,19 +39144,19 @@
       </c>
       <c r="AD71" s="35" t="str">
         <f t="shared" si="118"/>
-        <v>Ánh NV</v>
+        <v>Châu</v>
       </c>
       <c r="AE71" s="35" t="str">
         <f t="shared" si="119"/>
-        <v>GDĐP -6A1</v>
+        <v>Tiếng Trung -6A1</v>
       </c>
       <c r="AF71" s="35" t="str">
         <f t="shared" si="104"/>
-        <v>Nguyên</v>
+        <v>Ánh NV</v>
       </c>
       <c r="AG71" s="35" t="str">
         <f t="shared" si="105"/>
-        <v>Tin -7A1</v>
+        <v>Văn -7A1</v>
       </c>
       <c r="AH71" s="35" t="str">
         <f t="shared" si="106"/>
@@ -39297,11 +39291,11 @@
       </c>
       <c r="AF72" s="35" t="str">
         <f t="shared" si="104"/>
-        <v>Ánh NV</v>
+        <v>Phương Anh</v>
       </c>
       <c r="AG72" s="35" t="str">
         <f t="shared" si="105"/>
-        <v>Văn -7A1</v>
+        <v>HĐTN -7A1</v>
       </c>
       <c r="AH72" s="35" t="str">
         <f t="shared" si="106"/>
@@ -39567,11 +39561,11 @@
       </c>
       <c r="AD74" s="35" t="str">
         <f t="shared" si="118"/>
-        <v>Châu</v>
+        <v>Ánh NV</v>
       </c>
       <c r="AE74" s="35" t="str">
         <f t="shared" si="119"/>
-        <v>Tiếng Trung -6A1</v>
+        <v>GDĐP -6A1</v>
       </c>
       <c r="AF74" s="35" t="str">
         <f t="shared" si="104"/>
@@ -41366,7 +41360,7 @@
       </c>
       <c r="AB87" s="35" t="str">
         <f t="shared" si="102"/>
-        <v>Ly</v>
+        <v>Ngọc</v>
       </c>
       <c r="AC87" s="35" t="str">
         <f t="shared" si="103"/>
@@ -61153,7 +61147,7 @@
       </c>
       <c r="B507" s="29" t="str">
         <f t="shared" si="301"/>
-        <v>4Sáng2Ly</v>
+        <v>4Sáng2Ngọc</v>
       </c>
       <c r="C507" s="29" t="str">
         <f t="shared" si="302"/>
@@ -61177,7 +61171,7 @@
       </c>
       <c r="I507" s="36" t="str">
         <f t="shared" si="306"/>
-        <v>Ly</v>
+        <v>Ngọc</v>
       </c>
       <c r="J507" s="36" t="str">
         <f t="shared" si="307"/>
@@ -62825,7 +62819,7 @@
       </c>
       <c r="B551" s="29" t="str">
         <f t="shared" si="309"/>
-        <v>2Chiều1Nguyên</v>
+        <v>2Chiều1Ánh NV</v>
       </c>
       <c r="C551" s="29" t="str">
         <f t="shared" si="310"/>
@@ -62849,11 +62843,11 @@
       </c>
       <c r="I551" s="36" t="str">
         <f t="shared" si="314"/>
-        <v>Nguyên</v>
+        <v>Ánh NV</v>
       </c>
       <c r="J551" s="36" t="str">
         <f t="shared" si="315"/>
-        <v>Tin -7A1</v>
+        <v>Văn -7A1</v>
       </c>
     </row>
     <row r="552" spans="1:10" x14ac:dyDescent="0.25">
@@ -62863,7 +62857,7 @@
       </c>
       <c r="B552" s="29" t="str">
         <f t="shared" si="309"/>
-        <v>2Chiều2Ánh NV</v>
+        <v>2Chiều2Phương Anh</v>
       </c>
       <c r="C552" s="29" t="str">
         <f t="shared" si="310"/>
@@ -62887,11 +62881,11 @@
       </c>
       <c r="I552" s="36" t="str">
         <f t="shared" si="314"/>
-        <v>Ánh NV</v>
+        <v>Phương Anh</v>
       </c>
       <c r="J552" s="36" t="str">
         <f t="shared" si="315"/>
-        <v>Văn -7A1</v>
+        <v>HĐTN -7A1</v>
       </c>
     </row>
     <row r="553" spans="1:10" x14ac:dyDescent="0.25">
@@ -71945,7 +71939,7 @@
       </c>
       <c r="B791" s="29" t="str">
         <f t="shared" si="397"/>
-        <v>2Chiều1Ánh NV</v>
+        <v>2Chiều1Châu</v>
       </c>
       <c r="C791" s="29" t="str">
         <f t="shared" si="398"/>
@@ -71969,11 +71963,11 @@
       </c>
       <c r="I791" s="36" t="str">
         <f t="shared" ref="I791:J791" si="427">AD71</f>
-        <v>Ánh NV</v>
+        <v>Châu</v>
       </c>
       <c r="J791" s="36" t="str">
         <f t="shared" si="427"/>
-        <v>GDĐP -6A1</v>
+        <v>Tiếng Trung -6A1</v>
       </c>
     </row>
     <row r="792" spans="1:10" x14ac:dyDescent="0.25">
@@ -72059,7 +72053,7 @@
       </c>
       <c r="B794" s="29" t="str">
         <f t="shared" si="397"/>
-        <v>2Chiều4Châu</v>
+        <v>2Chiều4Ánh NV</v>
       </c>
       <c r="C794" s="29" t="str">
         <f t="shared" si="398"/>
@@ -72083,11 +72077,11 @@
       </c>
       <c r="I794" s="36" t="str">
         <f t="shared" ref="I794:J794" si="430">AD74</f>
-        <v>Châu</v>
+        <v>Ánh NV</v>
       </c>
       <c r="J794" s="36" t="str">
         <f t="shared" si="430"/>
-        <v>Tiếng Trung -6A1</v>
+        <v>GDĐP -6A1</v>
       </c>
     </row>
     <row r="795" spans="1:10" x14ac:dyDescent="0.25">
@@ -74031,26 +74025,87 @@
   </sheetData>
   <autoFilter ref="B65:K845" xr:uid="{02CDF078-79E2-734D-A2B9-67DD883EE2B5}"/>
   <mergeCells count="125">
-    <mergeCell ref="DH31:DH35"/>
-    <mergeCell ref="DG36:DG40"/>
-    <mergeCell ref="DH36:DH40"/>
-    <mergeCell ref="DH41:DH45"/>
-    <mergeCell ref="DG46:DG50"/>
-    <mergeCell ref="DH46:DH50"/>
-    <mergeCell ref="DG51:DG55"/>
-    <mergeCell ref="DH51:DH55"/>
-    <mergeCell ref="DG56:DG60"/>
-    <mergeCell ref="DH56:DH60"/>
-    <mergeCell ref="DG4:DG5"/>
-    <mergeCell ref="DI4:DI5"/>
-    <mergeCell ref="DG6:DG10"/>
-    <mergeCell ref="DH6:DH10"/>
-    <mergeCell ref="DH11:DH15"/>
-    <mergeCell ref="DG16:DG20"/>
-    <mergeCell ref="DH16:DH20"/>
-    <mergeCell ref="DH21:DH25"/>
-    <mergeCell ref="DG26:DG30"/>
-    <mergeCell ref="DH26:DH30"/>
+    <mergeCell ref="CG2:CI2"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="E1:I2"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="AA6:AA10"/>
+    <mergeCell ref="AA11:AA15"/>
+    <mergeCell ref="AA16:AA20"/>
+    <mergeCell ref="AA21:AA25"/>
+    <mergeCell ref="AA26:AA30"/>
+    <mergeCell ref="AA31:AA35"/>
+    <mergeCell ref="AA36:AA40"/>
+    <mergeCell ref="AA41:AA45"/>
+    <mergeCell ref="Z51:Z55"/>
+    <mergeCell ref="F6:F10"/>
+    <mergeCell ref="F11:F15"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="F26:F30"/>
+    <mergeCell ref="F31:F35"/>
+    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="E36:E40"/>
+    <mergeCell ref="E46:E50"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="AA46:AA50"/>
+    <mergeCell ref="AA51:AA55"/>
+    <mergeCell ref="Z56:Z60"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="AA56:AA60"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="F36:F40"/>
+    <mergeCell ref="F41:F45"/>
+    <mergeCell ref="F46:F50"/>
+    <mergeCell ref="Z6:Z10"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="Z16:Z20"/>
+    <mergeCell ref="Z26:Z30"/>
+    <mergeCell ref="Z36:Z40"/>
+    <mergeCell ref="Z46:Z50"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="BP56:BP60"/>
+    <mergeCell ref="AV31:AV35"/>
+    <mergeCell ref="AU36:AU40"/>
+    <mergeCell ref="AV36:AV40"/>
+    <mergeCell ref="AV41:AV45"/>
+    <mergeCell ref="AU46:AU50"/>
+    <mergeCell ref="AV46:AV50"/>
+    <mergeCell ref="AU16:AU20"/>
+    <mergeCell ref="AV16:AV20"/>
+    <mergeCell ref="AV21:AV25"/>
+    <mergeCell ref="AU26:AU30"/>
+    <mergeCell ref="AV26:AV30"/>
+    <mergeCell ref="AW4:AW5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AU6:AU10"/>
+    <mergeCell ref="AV6:AV10"/>
+    <mergeCell ref="AV11:AV15"/>
+    <mergeCell ref="BP6:BP10"/>
+    <mergeCell ref="BQ11:BQ15"/>
+    <mergeCell ref="BP16:BP20"/>
+    <mergeCell ref="BQ16:BQ20"/>
+    <mergeCell ref="AU51:AU55"/>
+    <mergeCell ref="AV51:AV55"/>
+    <mergeCell ref="AU56:AU60"/>
+    <mergeCell ref="AV56:AV60"/>
+    <mergeCell ref="BP46:BP50"/>
+    <mergeCell ref="BQ46:BQ50"/>
+    <mergeCell ref="BP51:BP55"/>
+    <mergeCell ref="BQ51:BQ55"/>
+    <mergeCell ref="BQ21:BQ25"/>
+    <mergeCell ref="BP26:BP30"/>
+    <mergeCell ref="BQ26:BQ30"/>
+    <mergeCell ref="BQ31:BQ35"/>
+    <mergeCell ref="BP36:BP40"/>
+    <mergeCell ref="BQ36:BQ40"/>
     <mergeCell ref="CH46:CH50"/>
     <mergeCell ref="CG51:CG55"/>
     <mergeCell ref="CH51:CH55"/>
@@ -74075,87 +74130,26 @@
     <mergeCell ref="BQ41:BQ45"/>
     <mergeCell ref="BR4:BR5"/>
     <mergeCell ref="BQ6:BQ10"/>
-    <mergeCell ref="BQ11:BQ15"/>
-    <mergeCell ref="BP16:BP20"/>
-    <mergeCell ref="BQ16:BQ20"/>
-    <mergeCell ref="AU51:AU55"/>
-    <mergeCell ref="AV51:AV55"/>
-    <mergeCell ref="AU56:AU60"/>
-    <mergeCell ref="AV56:AV60"/>
-    <mergeCell ref="BP46:BP50"/>
-    <mergeCell ref="BQ46:BQ50"/>
-    <mergeCell ref="BP51:BP55"/>
-    <mergeCell ref="BQ51:BQ55"/>
-    <mergeCell ref="BQ21:BQ25"/>
-    <mergeCell ref="BP26:BP30"/>
-    <mergeCell ref="BQ26:BQ30"/>
-    <mergeCell ref="BQ31:BQ35"/>
-    <mergeCell ref="BP36:BP40"/>
-    <mergeCell ref="BQ36:BQ40"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BP56:BP60"/>
-    <mergeCell ref="AV31:AV35"/>
-    <mergeCell ref="AU36:AU40"/>
-    <mergeCell ref="AV36:AV40"/>
-    <mergeCell ref="AV41:AV45"/>
-    <mergeCell ref="AU46:AU50"/>
-    <mergeCell ref="AV46:AV50"/>
-    <mergeCell ref="AU16:AU20"/>
-    <mergeCell ref="AV16:AV20"/>
-    <mergeCell ref="AV21:AV25"/>
-    <mergeCell ref="AU26:AU30"/>
-    <mergeCell ref="AV26:AV30"/>
-    <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AU6:AU10"/>
-    <mergeCell ref="AV6:AV10"/>
-    <mergeCell ref="AV11:AV15"/>
-    <mergeCell ref="BP6:BP10"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AA56:AA60"/>
-    <mergeCell ref="F51:F55"/>
-    <mergeCell ref="F36:F40"/>
-    <mergeCell ref="F41:F45"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="Z6:Z10"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="Z16:Z20"/>
-    <mergeCell ref="Z26:Z30"/>
-    <mergeCell ref="Z36:Z40"/>
-    <mergeCell ref="Z46:Z50"/>
-    <mergeCell ref="E26:E30"/>
-    <mergeCell ref="E36:E40"/>
-    <mergeCell ref="E46:E50"/>
-    <mergeCell ref="E51:E55"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="AA46:AA50"/>
-    <mergeCell ref="AA51:AA55"/>
-    <mergeCell ref="Z56:Z60"/>
-    <mergeCell ref="F56:F60"/>
-    <mergeCell ref="CG2:CI2"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="E1:I2"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="E56:E60"/>
-    <mergeCell ref="AA6:AA10"/>
-    <mergeCell ref="AA11:AA15"/>
-    <mergeCell ref="AA16:AA20"/>
-    <mergeCell ref="AA21:AA25"/>
-    <mergeCell ref="AA26:AA30"/>
-    <mergeCell ref="AA31:AA35"/>
-    <mergeCell ref="AA36:AA40"/>
-    <mergeCell ref="AA41:AA45"/>
-    <mergeCell ref="Z51:Z55"/>
-    <mergeCell ref="F6:F10"/>
-    <mergeCell ref="F11:F15"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="F26:F30"/>
-    <mergeCell ref="F31:F35"/>
-    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="DG4:DG5"/>
+    <mergeCell ref="DI4:DI5"/>
+    <mergeCell ref="DG6:DG10"/>
+    <mergeCell ref="DH6:DH10"/>
+    <mergeCell ref="DH11:DH15"/>
+    <mergeCell ref="DG16:DG20"/>
+    <mergeCell ref="DH16:DH20"/>
+    <mergeCell ref="DH21:DH25"/>
+    <mergeCell ref="DG26:DG30"/>
+    <mergeCell ref="DH26:DH30"/>
+    <mergeCell ref="DH31:DH35"/>
+    <mergeCell ref="DG36:DG40"/>
+    <mergeCell ref="DH36:DH40"/>
+    <mergeCell ref="DH41:DH45"/>
+    <mergeCell ref="DG46:DG50"/>
+    <mergeCell ref="DH46:DH50"/>
+    <mergeCell ref="DG51:DG55"/>
+    <mergeCell ref="DH51:DH55"/>
+    <mergeCell ref="DG56:DG60"/>
+    <mergeCell ref="DH56:DH60"/>
   </mergeCells>
   <conditionalFormatting sqref="AC6:AO60">
     <cfRule type="cellIs" dxfId="10" priority="13" operator="between">
